--- a/docs/experiment_metrics.xlsx
+++ b/docs/experiment_metrics.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -1002,124 +1002,544 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>baseline/Run1/CDD-CD-256</t>
+          <t>TAR-DCR/Run2/dcr_frozen/LEVIR-CD-256</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9869</v>
+        <v>0.8953</v>
       </c>
       <c r="C14" t="n">
-        <v>0.9889</v>
+        <v>0.9231</v>
       </c>
       <c r="D14" t="n">
-        <v>0.997</v>
+        <v>0.9909</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9879</v>
+        <v>0.909</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9761</v>
+        <v>0.8331</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9862</v>
+        <v>0.9041</v>
       </c>
       <c r="H14" t="n">
-        <v>36.081</v>
+        <v>29.107</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.113</v>
       </c>
       <c r="J14" t="n">
-        <v>16.2593</v>
+        <v>12.6062</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.48e-05</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>dcr</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>baseline/Run1/LEVIR-CD-256</t>
+          <t>TAR-DCR/Run2/dcr_frozen/SYSU-CD-256</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9121</v>
+        <v>0.7723</v>
       </c>
       <c r="C15" t="n">
-        <v>0.9303</v>
+        <v>0.8741</v>
       </c>
       <c r="D15" t="n">
-        <v>0.992</v>
+        <v>0.9201</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9211</v>
+        <v>0.8201000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8537</v>
+        <v>0.695</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9169</v>
+        <v>0.769</v>
       </c>
       <c r="H15" t="n">
-        <v>36.081</v>
+        <v>29.107</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.113</v>
       </c>
       <c r="J15" t="n">
-        <v>16.2593</v>
+        <v>12.6062</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.563e-05</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>dcr</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>baseline/Run1/SYSU-CD-256</t>
+          <t>TAR-DCR/Run2/full_frozen/LEVIR-CD-256</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7973</v>
+        <v>0.8998</v>
       </c>
       <c r="C16" t="n">
-        <v>0.8651</v>
+        <v>0.9191</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9229000000000001</v>
+        <v>0.9909</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8299</v>
+        <v>0.9094</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7092000000000001</v>
+        <v>0.8338</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7801</v>
+        <v>0.9045</v>
       </c>
       <c r="H16" t="n">
-        <v>36.081</v>
+        <v>29.57</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.576</v>
       </c>
       <c r="J16" t="n">
-        <v>16.2593</v>
+        <v>12.6062</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.48e-05</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>TAR-DCR/Run2/full_frozen/SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.7948</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.8579</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.9206</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.8252</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.7023</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.7739</v>
+      </c>
+      <c r="H17" t="n">
+        <v>29.57</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.576</v>
+      </c>
+      <c r="J17" t="n">
+        <v>12.6062</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1.049e-05</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>TAR-DCR/Run2/full_last2/CDD-CD-256</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.9849</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.9835</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.9961</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.9842</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.9689</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.982</v>
+      </c>
+      <c r="H18" t="n">
+        <v>29.57</v>
+      </c>
+      <c r="I18" t="n">
+        <v>27.456</v>
+      </c>
+      <c r="J18" t="n">
+        <v>12.6062</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4.911e-05</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>TAR-DCR/Run2/full_last2/LEVIR-CD-256</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.9032</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.926</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.9913999999999999</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.9144</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.8424</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.9099</v>
+      </c>
+      <c r="H19" t="n">
+        <v>29.57</v>
+      </c>
+      <c r="I19" t="n">
+        <v>27.456</v>
+      </c>
+      <c r="J19" t="n">
+        <v>12.6062</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.098e-05</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>TAR-DCR/Run2/full_last2/SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.7956</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.8774999999999999</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.9256</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.8345</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.716</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.7866</v>
+      </c>
+      <c r="H20" t="n">
+        <v>29.57</v>
+      </c>
+      <c r="I20" t="n">
+        <v>27.456</v>
+      </c>
+      <c r="J20" t="n">
+        <v>12.6062</v>
+      </c>
+      <c r="K20" t="n">
+        <v>5.484e-06</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>TAR-DCR/Run2/full_last2/WHU-CD-256</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0.9435</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.9595</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.9962</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.9514</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.9074</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.9494</v>
+      </c>
+      <c r="H21" t="n">
+        <v>29.57</v>
+      </c>
+      <c r="I21" t="n">
+        <v>27.456</v>
+      </c>
+      <c r="J21" t="n">
+        <v>12.6062</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1.049e-05</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>TAR-DCR/Run2/no_residual/LEVIR-CD-256</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0.8925</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.9287</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.991</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.9102</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.8352000000000001</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.9055</v>
+      </c>
+      <c r="H22" t="n">
+        <v>29.57</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1.576</v>
+      </c>
+      <c r="J22" t="n">
+        <v>12.6062</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2.48e-05</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>TAR-DCR/Run2/no_residual/SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0.7672</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.8723</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.9186</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.8163</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.6897</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.7643</v>
+      </c>
+      <c r="H23" t="n">
+        <v>29.57</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.576</v>
+      </c>
+      <c r="J23" t="n">
+        <v>12.6062</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.861e-06</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>baseline/Run1/CDD-CD-256</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0.9869</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.9889</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.997</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9879</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.9761</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.9862</v>
+      </c>
+      <c r="H24" t="n">
+        <v>36.081</v>
+      </c>
+      <c r="J24" t="n">
+        <v>16.2593</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>baseline/Run1/LEVIR-CD-256</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0.9121</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.9303</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.992</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.9211</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.8537</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.9169</v>
+      </c>
+      <c r="H25" t="n">
+        <v>36.081</v>
+      </c>
+      <c r="J25" t="n">
+        <v>16.2593</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>baseline/Run1/SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0.7973</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.8651</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.9229000000000001</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.8299</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.7092000000000001</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.7801</v>
+      </c>
+      <c r="H26" t="n">
+        <v>36.081</v>
+      </c>
+      <c r="J26" t="n">
+        <v>16.2593</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>baseline/Run1/WHU-CD-256</t>
         </is>
       </c>
-      <c r="B17" t="n">
+      <c r="B27" t="n">
         <v>0.9328</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C27" t="n">
         <v>0.9679</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D27" t="n">
         <v>0.9961</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E27" t="n">
         <v>0.95</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F27" t="n">
         <v>0.9046999999999999</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G27" t="n">
         <v>0.948</v>
       </c>
-      <c r="H17" t="n">
+      <c r="H27" t="n">
         <v>36.081</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J27" t="n">
         <v>16.2593</v>
       </c>
     </row>

--- a/docs/experiment_metrics.xlsx
+++ b/docs/experiment_metrics.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="metrics" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'metrics'!$A$1:$O$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'metrics'!$A$1:$O$35</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O31"/>
+  <dimension ref="A1:O35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1987,12 +1987,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>TAR-DCR</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run4</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
@@ -2002,41 +2002,50 @@
         </is>
       </c>
       <c r="E28" s="2" t="n">
-        <v>98.69</v>
+        <v>98.44</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>98.89</v>
+        <v>98.34999999999999</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>99.7</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>98.79000000000001</v>
+        <v>98.39</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>97.61</v>
+        <v>96.84</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>98.62</v>
+        <v>98.17</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>36.081</v>
-      </c>
-      <c r="L28" s="2" t="n"/>
+        <v>29.57</v>
+      </c>
+      <c r="L28" s="2" t="n">
+        <v>27.457</v>
+      </c>
       <c r="M28" s="2" t="n">
-        <v>16.2593</v>
-      </c>
-      <c r="N28" s="3" t="n"/>
+        <v>12.6062</v>
+      </c>
+      <c r="N28" s="3" t="n">
+        <v>3.815e-05</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>TAR-DCR</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run4</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
@@ -2046,41 +2055,50 @@
         </is>
       </c>
       <c r="E29" s="2" t="n">
-        <v>91.20999999999999</v>
+        <v>90.23</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>93.03</v>
+        <v>92.69</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>99.2</v>
+        <v>99.14</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>92.11</v>
+        <v>91.45</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>85.37</v>
+        <v>84.23999999999999</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>91.69</v>
+        <v>90.98999999999999</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>36.081</v>
-      </c>
-      <c r="L29" s="2" t="n"/>
+        <v>29.57</v>
+      </c>
+      <c r="L29" s="2" t="n">
+        <v>27.457</v>
+      </c>
       <c r="M29" s="2" t="n">
-        <v>16.2593</v>
-      </c>
-      <c r="N29" s="3" t="n"/>
+        <v>12.6062</v>
+      </c>
+      <c r="N29" s="3" t="n">
+        <v>2.766e-05</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>TAR-DCR</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run4</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
@@ -2090,41 +2108,50 @@
         </is>
       </c>
       <c r="E30" s="2" t="n">
-        <v>79.73</v>
+        <v>79.19</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>86.51000000000001</v>
+        <v>87.72</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>92.29000000000001</v>
+        <v>92.48</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>82.98999999999999</v>
+        <v>83.23999999999999</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>70.92</v>
+        <v>71.29000000000001</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>78.01000000000001</v>
+        <v>78.41</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>36.081</v>
-      </c>
-      <c r="L30" s="2" t="n"/>
+        <v>29.57</v>
+      </c>
+      <c r="L30" s="2" t="n">
+        <v>27.457</v>
+      </c>
       <c r="M30" s="2" t="n">
-        <v>16.2593</v>
-      </c>
-      <c r="N30" s="3" t="n"/>
+        <v>12.6062</v>
+      </c>
+      <c r="N30" s="3" t="n">
+        <v>1.049e-05</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>TAR-DCR</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run4</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
@@ -2134,34 +2161,219 @@
         </is>
       </c>
       <c r="E31" s="2" t="n">
+        <v>93.7</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>99.62</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>95.08</v>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>90.62</v>
+      </c>
+      <c r="J31" s="2" t="n">
+        <v>94.88</v>
+      </c>
+      <c r="K31" s="2" t="n">
+        <v>29.57</v>
+      </c>
+      <c r="L31" s="2" t="n">
+        <v>27.457</v>
+      </c>
+      <c r="M31" s="2" t="n">
+        <v>12.6062</v>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v>8.583000000000001e-06</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>CDD-CD-256</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>98.69</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>98.89</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>98.79000000000001</v>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>97.61</v>
+      </c>
+      <c r="J32" s="2" t="n">
+        <v>98.62</v>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>36.081</v>
+      </c>
+      <c r="L32" s="2" t="n"/>
+      <c r="M32" s="2" t="n">
+        <v>16.2593</v>
+      </c>
+      <c r="N32" s="3" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LEVIR-CD-256</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>91.20999999999999</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>93.03</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>92.11</v>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>85.37</v>
+      </c>
+      <c r="J33" s="2" t="n">
+        <v>91.69</v>
+      </c>
+      <c r="K33" s="2" t="n">
+        <v>36.081</v>
+      </c>
+      <c r="L33" s="2" t="n"/>
+      <c r="M33" s="2" t="n">
+        <v>16.2593</v>
+      </c>
+      <c r="N33" s="3" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>79.73</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>86.51000000000001</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>92.29000000000001</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>82.98999999999999</v>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>70.92</v>
+      </c>
+      <c r="J34" s="2" t="n">
+        <v>78.01000000000001</v>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>36.081</v>
+      </c>
+      <c r="L34" s="2" t="n"/>
+      <c r="M34" s="2" t="n">
+        <v>16.2593</v>
+      </c>
+      <c r="N34" s="3" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>WHU-CD-256</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="n">
         <v>93.28</v>
       </c>
-      <c r="F31" s="2" t="n">
+      <c r="F35" s="2" t="n">
         <v>96.79000000000001</v>
       </c>
-      <c r="G31" s="2" t="n">
+      <c r="G35" s="2" t="n">
         <v>99.61</v>
       </c>
-      <c r="H31" s="2" t="n">
+      <c r="H35" s="2" t="n">
         <v>95</v>
       </c>
-      <c r="I31" s="2" t="n">
+      <c r="I35" s="2" t="n">
         <v>90.47</v>
       </c>
-      <c r="J31" s="2" t="n">
+      <c r="J35" s="2" t="n">
         <v>94.8</v>
       </c>
-      <c r="K31" s="2" t="n">
+      <c r="K35" s="2" t="n">
         <v>36.081</v>
       </c>
-      <c r="L31" s="2" t="n"/>
-      <c r="M31" s="2" t="n">
+      <c r="L35" s="2" t="n"/>
+      <c r="M35" s="2" t="n">
         <v>16.2593</v>
       </c>
-      <c r="N31" s="3" t="n"/>
+      <c r="N35" s="3" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O31"/>
+  <autoFilter ref="A1:O35"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/experiment_metrics.xlsx
+++ b/docs/experiment_metrics.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="metrics" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'metrics'!$A$1:$O$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'metrics'!$A$1:$P$38</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O35"/>
+  <dimension ref="A1:P38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -434,11 +434,12 @@
     <col width="8" customWidth="1" min="8" max="8"/>
     <col width="8" customWidth="1" min="9" max="9"/>
     <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -494,25 +495,30 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Params(M)</t>
+          <t>TrainGraphParams(M)</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Trainable(M)</t>
+          <t>TrainableParams(M)</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>FLOPs(G)</t>
+          <t>DeployParams(M)</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>DeployFLOPs(G)</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>ReparamErr</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>RepMode</t>
         </is>
@@ -564,12 +570,15 @@
         <v>0.838</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>12.6062</v>
-      </c>
-      <c r="N2" s="3" t="n">
+        <v>28.829</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>12.6062</v>
+      </c>
+      <c r="O2" s="3" t="n">
         <v>2.241e-05</v>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>plain</t>
         </is>
@@ -621,12 +630,15 @@
         <v>0.838</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>12.6062</v>
-      </c>
-      <c r="N3" s="3" t="n">
+        <v>28.829</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>12.6062</v>
+      </c>
+      <c r="O3" s="3" t="n">
         <v>2.098e-05</v>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>plain</t>
         </is>
@@ -678,12 +690,15 @@
         <v>0.838</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>12.6062</v>
-      </c>
-      <c r="N4" s="3" t="n">
+        <v>28.829</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>12.6062</v>
+      </c>
+      <c r="O4" s="3" t="n">
         <v>1.335e-05</v>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>plain</t>
         </is>
@@ -735,12 +750,15 @@
         <v>0.838</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>12.6062</v>
-      </c>
-      <c r="N5" s="3" t="n">
+        <v>28.829</v>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>12.6062</v>
+      </c>
+      <c r="O5" s="3" t="n">
         <v>1.049e-05</v>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>plain</t>
         </is>
@@ -792,12 +810,15 @@
         <v>1.299</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>12.6062</v>
-      </c>
-      <c r="N6" s="3" t="n">
+        <v>28.829</v>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>12.6062</v>
+      </c>
+      <c r="O6" s="3" t="n">
         <v>1.574e-05</v>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>tar</t>
         </is>
@@ -849,12 +870,15 @@
         <v>1.299</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>12.6062</v>
-      </c>
-      <c r="N7" s="3" t="n">
+        <v>28.829</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>12.6062</v>
+      </c>
+      <c r="O7" s="3" t="n">
         <v>1.001e-05</v>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>tar</t>
         </is>
@@ -906,12 +930,15 @@
         <v>1.299</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>12.6062</v>
-      </c>
-      <c r="N8" s="3" t="n">
+        <v>28.829</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>12.6062</v>
+      </c>
+      <c r="O8" s="3" t="n">
         <v>2.003e-05</v>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>tar</t>
         </is>
@@ -963,12 +990,15 @@
         <v>1.299</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>12.6062</v>
-      </c>
-      <c r="N9" s="3" t="n">
+        <v>28.829</v>
+      </c>
+      <c r="N9" s="2" t="n">
+        <v>12.6062</v>
+      </c>
+      <c r="O9" s="3" t="n">
         <v>1.144e-05</v>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>tar</t>
         </is>
@@ -1020,12 +1050,15 @@
         <v>1.564</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>12.6062</v>
-      </c>
-      <c r="N10" s="3" t="n">
+        <v>28.829</v>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v>12.6062</v>
+      </c>
+      <c r="O10" s="3" t="n">
         <v>5.722e-05</v>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>full</t>
         </is>
@@ -1077,12 +1110,15 @@
         <v>1.564</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>12.6062</v>
-      </c>
-      <c r="N11" s="3" t="n">
+        <v>28.829</v>
+      </c>
+      <c r="N11" s="2" t="n">
+        <v>12.6062</v>
+      </c>
+      <c r="O11" s="3" t="n">
         <v>0.0001106</v>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>full</t>
         </is>
@@ -1134,12 +1170,15 @@
         <v>1.564</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>12.6062</v>
-      </c>
-      <c r="N12" s="3" t="n">
+        <v>28.829</v>
+      </c>
+      <c r="N12" s="2" t="n">
+        <v>12.6062</v>
+      </c>
+      <c r="O12" s="3" t="n">
         <v>1.626e-05</v>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>full</t>
         </is>
@@ -1191,12 +1230,15 @@
         <v>1.564</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>12.6062</v>
-      </c>
-      <c r="N13" s="3" t="n">
+        <v>28.829</v>
+      </c>
+      <c r="N13" s="2" t="n">
+        <v>12.6062</v>
+      </c>
+      <c r="O13" s="3" t="n">
         <v>6.199e-06</v>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>full</t>
         </is>
@@ -1248,12 +1290,15 @@
         <v>1.113</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>12.6062</v>
-      </c>
-      <c r="N14" s="3" t="n">
+        <v>28.829</v>
+      </c>
+      <c r="N14" s="2" t="n">
+        <v>12.6062</v>
+      </c>
+      <c r="O14" s="3" t="n">
         <v>2.48e-05</v>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>dcr</t>
         </is>
@@ -1305,12 +1350,15 @@
         <v>1.113</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>12.6062</v>
-      </c>
-      <c r="N15" s="3" t="n">
+        <v>28.829</v>
+      </c>
+      <c r="N15" s="2" t="n">
+        <v>12.6062</v>
+      </c>
+      <c r="O15" s="3" t="n">
         <v>2.563e-05</v>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>dcr</t>
         </is>
@@ -1362,12 +1410,15 @@
         <v>1.576</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>12.6062</v>
-      </c>
-      <c r="N16" s="3" t="n">
+        <v>28.829</v>
+      </c>
+      <c r="N16" s="2" t="n">
+        <v>12.6062</v>
+      </c>
+      <c r="O16" s="3" t="n">
         <v>2.48e-05</v>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>full</t>
         </is>
@@ -1419,12 +1470,15 @@
         <v>1.576</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>12.6062</v>
-      </c>
-      <c r="N17" s="3" t="n">
+        <v>28.829</v>
+      </c>
+      <c r="N17" s="2" t="n">
+        <v>12.6062</v>
+      </c>
+      <c r="O17" s="3" t="n">
         <v>1.049e-05</v>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>full</t>
         </is>
@@ -1476,12 +1530,15 @@
         <v>27.456</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>12.6062</v>
-      </c>
-      <c r="N18" s="3" t="n">
+        <v>28.829</v>
+      </c>
+      <c r="N18" s="2" t="n">
+        <v>12.6062</v>
+      </c>
+      <c r="O18" s="3" t="n">
         <v>4.911e-05</v>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>full</t>
         </is>
@@ -1533,12 +1590,15 @@
         <v>27.456</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>12.6062</v>
-      </c>
-      <c r="N19" s="3" t="n">
+        <v>28.829</v>
+      </c>
+      <c r="N19" s="2" t="n">
+        <v>12.6062</v>
+      </c>
+      <c r="O19" s="3" t="n">
         <v>2.098e-05</v>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>full</t>
         </is>
@@ -1590,12 +1650,15 @@
         <v>27.456</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>12.6062</v>
-      </c>
-      <c r="N20" s="3" t="n">
+        <v>28.829</v>
+      </c>
+      <c r="N20" s="2" t="n">
+        <v>12.6062</v>
+      </c>
+      <c r="O20" s="3" t="n">
         <v>5.484e-06</v>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>full</t>
         </is>
@@ -1647,12 +1710,15 @@
         <v>27.456</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>12.6062</v>
-      </c>
-      <c r="N21" s="3" t="n">
+        <v>28.829</v>
+      </c>
+      <c r="N21" s="2" t="n">
+        <v>12.6062</v>
+      </c>
+      <c r="O21" s="3" t="n">
         <v>1.049e-05</v>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>full</t>
         </is>
@@ -1704,12 +1770,15 @@
         <v>1.576</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>12.6062</v>
-      </c>
-      <c r="N22" s="3" t="n">
+        <v>28.829</v>
+      </c>
+      <c r="N22" s="2" t="n">
+        <v>12.6062</v>
+      </c>
+      <c r="O22" s="3" t="n">
         <v>2.48e-05</v>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>full</t>
         </is>
@@ -1761,12 +1830,15 @@
         <v>1.576</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>12.6062</v>
-      </c>
-      <c r="N23" s="3" t="n">
+        <v>28.829</v>
+      </c>
+      <c r="N23" s="2" t="n">
+        <v>12.6062</v>
+      </c>
+      <c r="O23" s="3" t="n">
         <v>2.861e-06</v>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>full</t>
         </is>
@@ -1814,12 +1886,15 @@
         <v>27.457</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>12.6062</v>
-      </c>
-      <c r="N24" s="3" t="n">
+        <v>28.829</v>
+      </c>
+      <c r="N24" s="2" t="n">
+        <v>12.6062</v>
+      </c>
+      <c r="O24" s="3" t="n">
         <v>7.248e-05</v>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>full</t>
         </is>
@@ -1867,12 +1942,15 @@
         <v>27.457</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>12.6062</v>
-      </c>
-      <c r="N25" s="3" t="n">
+        <v>28.829</v>
+      </c>
+      <c r="N25" s="2" t="n">
+        <v>12.6062</v>
+      </c>
+      <c r="O25" s="3" t="n">
         <v>2.003e-05</v>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>full</t>
         </is>
@@ -1920,12 +1998,15 @@
         <v>27.457</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>12.6062</v>
-      </c>
-      <c r="N26" s="3" t="n">
+        <v>28.829</v>
+      </c>
+      <c r="N26" s="2" t="n">
+        <v>12.6062</v>
+      </c>
+      <c r="O26" s="3" t="n">
         <v>1.335e-05</v>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>full</t>
         </is>
@@ -1973,12 +2054,15 @@
         <v>27.457</v>
       </c>
       <c r="M27" s="2" t="n">
-        <v>12.6062</v>
-      </c>
-      <c r="N27" s="3" t="n">
+        <v>28.829</v>
+      </c>
+      <c r="N27" s="2" t="n">
+        <v>12.6062</v>
+      </c>
+      <c r="O27" s="3" t="n">
         <v>1.049e-05</v>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>full</t>
         </is>
@@ -2026,12 +2110,15 @@
         <v>27.457</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>12.6062</v>
-      </c>
-      <c r="N28" s="3" t="n">
+        <v>28.829</v>
+      </c>
+      <c r="N28" s="2" t="n">
+        <v>12.6062</v>
+      </c>
+      <c r="O28" s="3" t="n">
         <v>3.815e-05</v>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>full</t>
         </is>
@@ -2079,12 +2166,15 @@
         <v>27.457</v>
       </c>
       <c r="M29" s="2" t="n">
-        <v>12.6062</v>
-      </c>
-      <c r="N29" s="3" t="n">
+        <v>28.829</v>
+      </c>
+      <c r="N29" s="2" t="n">
+        <v>12.6062</v>
+      </c>
+      <c r="O29" s="3" t="n">
         <v>2.766e-05</v>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="P29" t="inlineStr">
         <is>
           <t>full</t>
         </is>
@@ -2132,12 +2222,15 @@
         <v>27.457</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>12.6062</v>
-      </c>
-      <c r="N30" s="3" t="n">
+        <v>28.829</v>
+      </c>
+      <c r="N30" s="2" t="n">
+        <v>12.6062</v>
+      </c>
+      <c r="O30" s="3" t="n">
         <v>1.049e-05</v>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>full</t>
         </is>
@@ -2185,12 +2278,15 @@
         <v>27.457</v>
       </c>
       <c r="M31" s="2" t="n">
-        <v>12.6062</v>
-      </c>
-      <c r="N31" s="3" t="n">
+        <v>28.829</v>
+      </c>
+      <c r="N31" s="2" t="n">
+        <v>12.6062</v>
+      </c>
+      <c r="O31" s="3" t="n">
         <v>8.583000000000001e-06</v>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>full</t>
         </is>
@@ -2199,134 +2295,182 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>TAR-DCR</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
+          <t>Run5</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>C1_swap_only</t>
+        </is>
+      </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E32" s="2" t="n">
-        <v>98.69</v>
+        <v>90.43000000000001</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>98.89</v>
+        <v>92.45</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>99.7</v>
+        <v>99.14</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>98.79000000000001</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>97.61</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>98.62</v>
+        <v>90.97</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>36.081</v>
-      </c>
-      <c r="L32" s="2" t="n"/>
+        <v>29.57</v>
+      </c>
+      <c r="L32" s="2" t="n">
+        <v>27.456</v>
+      </c>
       <c r="M32" s="2" t="n">
-        <v>16.2593</v>
-      </c>
-      <c r="N32" s="3" t="n"/>
+        <v>28.829</v>
+      </c>
+      <c r="N32" s="2" t="n">
+        <v>12.6062</v>
+      </c>
+      <c r="O32" s="3" t="n">
+        <v>1.621e-05</v>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>TAR-DCR</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
+          <t>Run5</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>D0_full_encoder</t>
+        </is>
+      </c>
       <c r="D33" t="inlineStr">
         <is>
           <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E33" s="2" t="n">
-        <v>91.20999999999999</v>
+        <v>90.56</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>93.03</v>
+        <v>92.81999999999999</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>99.2</v>
+        <v>99.16</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>92.11</v>
+        <v>91.68000000000001</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>85.37</v>
+        <v>84.63</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>91.69</v>
+        <v>91.23999999999999</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>36.081</v>
-      </c>
-      <c r="L33" s="2" t="n"/>
+        <v>29.57</v>
+      </c>
+      <c r="L33" s="2" t="n">
+        <v>29.57</v>
+      </c>
       <c r="M33" s="2" t="n">
-        <v>16.2593</v>
-      </c>
-      <c r="N33" s="3" t="n"/>
+        <v>28.829</v>
+      </c>
+      <c r="N33" s="2" t="n">
+        <v>12.6062</v>
+      </c>
+      <c r="O33" s="3" t="n">
+        <v>1.431e-05</v>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>TAR-DCR</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr"/>
+          <t>Run5</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>M1_BOTR</t>
+        </is>
+      </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E34" s="2" t="n">
-        <v>79.73</v>
+        <v>90.45999999999999</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>86.51000000000001</v>
+        <v>92.44</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>92.29000000000001</v>
+        <v>99.14</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>82.98999999999999</v>
+        <v>91.44</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>70.92</v>
+        <v>84.23</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>78.01000000000001</v>
+        <v>90.98999999999999</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>36.081</v>
-      </c>
-      <c r="L34" s="2" t="n"/>
+        <v>30.032</v>
+      </c>
+      <c r="L34" s="2" t="n">
+        <v>27.918</v>
+      </c>
       <c r="M34" s="2" t="n">
-        <v>16.2593</v>
-      </c>
-      <c r="N34" s="3" t="n"/>
+        <v>28.829</v>
+      </c>
+      <c r="N34" s="2" t="n">
+        <v>12.6062</v>
+      </c>
+      <c r="O34" s="3" t="n">
+        <v>1.526e-05</v>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2342,38 +2486,182 @@
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E35" s="2" t="n">
-        <v>93.28</v>
+        <v>98.69</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>96.79000000000001</v>
+        <v>98.89</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>99.61</v>
+        <v>99.7</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>95</v>
+        <v>98.79000000000001</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>90.47</v>
+        <v>97.61</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>94.8</v>
+        <v>98.62</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>36.081</v>
       </c>
       <c r="L35" s="2" t="n"/>
       <c r="M35" s="2" t="n">
+        <v>36.081</v>
+      </c>
+      <c r="N35" s="2" t="n">
         <v>16.2593</v>
       </c>
-      <c r="N35" s="3" t="n"/>
+      <c r="O35" s="3" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LEVIR-CD-256</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>91.20999999999999</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>93.03</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>92.11</v>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>85.37</v>
+      </c>
+      <c r="J36" s="2" t="n">
+        <v>91.69</v>
+      </c>
+      <c r="K36" s="2" t="n">
+        <v>36.081</v>
+      </c>
+      <c r="L36" s="2" t="n"/>
+      <c r="M36" s="2" t="n">
+        <v>36.081</v>
+      </c>
+      <c r="N36" s="2" t="n">
+        <v>16.2593</v>
+      </c>
+      <c r="O36" s="3" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>79.73</v>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>86.51000000000001</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>92.29000000000001</v>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>82.98999999999999</v>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>70.92</v>
+      </c>
+      <c r="J37" s="2" t="n">
+        <v>78.01000000000001</v>
+      </c>
+      <c r="K37" s="2" t="n">
+        <v>36.081</v>
+      </c>
+      <c r="L37" s="2" t="n"/>
+      <c r="M37" s="2" t="n">
+        <v>36.081</v>
+      </c>
+      <c r="N37" s="2" t="n">
+        <v>16.2593</v>
+      </c>
+      <c r="O37" s="3" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>WHU-CD-256</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>93.28</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>96.79000000000001</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>99.61</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>90.47</v>
+      </c>
+      <c r="J38" s="2" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="K38" s="2" t="n">
+        <v>36.081</v>
+      </c>
+      <c r="L38" s="2" t="n"/>
+      <c r="M38" s="2" t="n">
+        <v>36.081</v>
+      </c>
+      <c r="N38" s="2" t="n">
+        <v>16.2593</v>
+      </c>
+      <c r="O38" s="3" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O35"/>
+  <autoFilter ref="A1:P38"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/experiment_metrics.xlsx
+++ b/docs/experiment_metrics.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="metrics" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'metrics'!$A$1:$P$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'metrics'!$A$1:$T$42</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P38"/>
+  <dimension ref="A1:T42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -440,6 +440,10 @@
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="6" customWidth="1" min="17" max="17"/>
+    <col width="6" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -523,6 +527,26 @@
           <t>RepMode</t>
         </is>
       </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Botr</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>NSCR</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>NSCRScope</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>EncoderTrain</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2351,6 +2375,14 @@
           <t>full</t>
         </is>
       </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>last2</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2411,6 +2443,14 @@
           <t>full</t>
         </is>
       </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2471,197 +2511,509 @@
           <t>full</t>
         </is>
       </c>
+      <c r="Q34" t="n">
+        <v>1</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>last2</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>TAR-DCR</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr"/>
+          <t>Run6</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>M1_NSCR_high2</t>
+        </is>
+      </c>
       <c r="D35" t="inlineStr">
         <is>
           <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E35" s="2" t="n">
-        <v>98.69</v>
+        <v>98.42</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>98.89</v>
+        <v>98.36</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>99.7</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>98.79000000000001</v>
+        <v>98.39</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>97.61</v>
+        <v>96.83</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>98.62</v>
+        <v>98.16</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>36.081</v>
-      </c>
-      <c r="L35" s="2" t="n"/>
+        <v>29.572</v>
+      </c>
+      <c r="L35" s="2" t="n">
+        <v>27.458</v>
+      </c>
       <c r="M35" s="2" t="n">
-        <v>36.081</v>
+        <v>28.829</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>16.2593</v>
-      </c>
-      <c r="O35" s="3" t="n"/>
+        <v>12.6062</v>
+      </c>
+      <c r="O35" s="3" t="n">
+        <v>3.529e-05</v>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>high2</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>last2</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>TAR-DCR</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr"/>
+          <t>Run6</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>M1_NSCR_high2</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr">
         <is>
           <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E36" s="2" t="n">
-        <v>91.20999999999999</v>
+        <v>90.73</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>93.03</v>
+        <v>92.08</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>99.2</v>
+        <v>99.13</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>92.11</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>85.37</v>
+        <v>84.16</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>91.69</v>
+        <v>90.94</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>36.081</v>
-      </c>
-      <c r="L36" s="2" t="n"/>
+        <v>29.572</v>
+      </c>
+      <c r="L36" s="2" t="n">
+        <v>27.458</v>
+      </c>
       <c r="M36" s="2" t="n">
-        <v>36.081</v>
+        <v>28.829</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>16.2593</v>
-      </c>
-      <c r="O36" s="3" t="n"/>
+        <v>12.6062</v>
+      </c>
+      <c r="O36" s="3" t="n">
+        <v>2.289e-05</v>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>high2</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>last2</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>TAR-DCR</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr"/>
+          <t>Run6</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>M1_NSCR_high2</t>
+        </is>
+      </c>
       <c r="D37" t="inlineStr">
         <is>
           <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E37" s="2" t="n">
-        <v>79.73</v>
+        <v>79.01000000000001</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>86.51000000000001</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>92.29000000000001</v>
+        <v>92.56999999999999</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>82.98999999999999</v>
+        <v>83.37</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>70.92</v>
+        <v>71.48</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>78.01000000000001</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>36.081</v>
-      </c>
-      <c r="L37" s="2" t="n"/>
+        <v>29.572</v>
+      </c>
+      <c r="L37" s="2" t="n">
+        <v>27.458</v>
+      </c>
       <c r="M37" s="2" t="n">
-        <v>36.081</v>
+        <v>28.829</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>16.2593</v>
-      </c>
-      <c r="O37" s="3" t="n"/>
+        <v>12.6062</v>
+      </c>
+      <c r="O37" s="3" t="n">
+        <v>5.722e-06</v>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>high2</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>last2</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>TAR-DCR</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr"/>
+          <t>Run6</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>M1_NSCR_high2</t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr">
         <is>
           <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E38" s="2" t="n">
-        <v>93.28</v>
+        <v>94.26000000000001</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>96.79000000000001</v>
+        <v>95.95999999999999</v>
       </c>
       <c r="G38" s="2" t="n">
         <v>99.61</v>
       </c>
       <c r="H38" s="2" t="n">
+        <v>95.09999999999999</v>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>90.66</v>
+      </c>
+      <c r="J38" s="2" t="n">
+        <v>94.90000000000001</v>
+      </c>
+      <c r="K38" s="2" t="n">
+        <v>29.572</v>
+      </c>
+      <c r="L38" s="2" t="n">
+        <v>27.458</v>
+      </c>
+      <c r="M38" s="2" t="n">
+        <v>28.829</v>
+      </c>
+      <c r="N38" s="2" t="n">
+        <v>12.6062</v>
+      </c>
+      <c r="O38" s="3" t="n">
+        <v>1.526e-05</v>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>high2</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>last2</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>CDD-CD-256</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>98.69</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>98.89</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>98.79000000000001</v>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>97.61</v>
+      </c>
+      <c r="J39" s="2" t="n">
+        <v>98.62</v>
+      </c>
+      <c r="K39" s="2" t="n">
+        <v>36.081</v>
+      </c>
+      <c r="L39" s="2" t="n"/>
+      <c r="M39" s="2" t="n">
+        <v>36.081</v>
+      </c>
+      <c r="N39" s="2" t="n">
+        <v>16.2593</v>
+      </c>
+      <c r="O39" s="3" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LEVIR-CD-256</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>91.20999999999999</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>93.03</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>92.11</v>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>85.37</v>
+      </c>
+      <c r="J40" s="2" t="n">
+        <v>91.69</v>
+      </c>
+      <c r="K40" s="2" t="n">
+        <v>36.081</v>
+      </c>
+      <c r="L40" s="2" t="n"/>
+      <c r="M40" s="2" t="n">
+        <v>36.081</v>
+      </c>
+      <c r="N40" s="2" t="n">
+        <v>16.2593</v>
+      </c>
+      <c r="O40" s="3" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>79.73</v>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>86.51000000000001</v>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>92.29000000000001</v>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>82.98999999999999</v>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>70.92</v>
+      </c>
+      <c r="J41" s="2" t="n">
+        <v>78.01000000000001</v>
+      </c>
+      <c r="K41" s="2" t="n">
+        <v>36.081</v>
+      </c>
+      <c r="L41" s="2" t="n"/>
+      <c r="M41" s="2" t="n">
+        <v>36.081</v>
+      </c>
+      <c r="N41" s="2" t="n">
+        <v>16.2593</v>
+      </c>
+      <c r="O41" s="3" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>WHU-CD-256</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>93.28</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>96.79000000000001</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>99.61</v>
+      </c>
+      <c r="H42" s="2" t="n">
         <v>95</v>
       </c>
-      <c r="I38" s="2" t="n">
+      <c r="I42" s="2" t="n">
         <v>90.47</v>
       </c>
-      <c r="J38" s="2" t="n">
+      <c r="J42" s="2" t="n">
         <v>94.8</v>
       </c>
-      <c r="K38" s="2" t="n">
+      <c r="K42" s="2" t="n">
         <v>36.081</v>
       </c>
-      <c r="L38" s="2" t="n"/>
-      <c r="M38" s="2" t="n">
+      <c r="L42" s="2" t="n"/>
+      <c r="M42" s="2" t="n">
         <v>36.081</v>
       </c>
-      <c r="N38" s="2" t="n">
+      <c r="N42" s="2" t="n">
         <v>16.2593</v>
       </c>
-      <c r="O38" s="3" t="n"/>
+      <c r="O42" s="3" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P38"/>
+  <autoFilter ref="A1:T42"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/experiment_metrics.xlsx
+++ b/docs/experiment_metrics.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="metrics" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'metrics'!$A$1:$T$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'metrics'!$A$1:$W$46</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T42"/>
+  <dimension ref="A1:W46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -444,6 +444,9 @@
     <col width="6" customWidth="1" min="18" max="18"/>
     <col width="10" customWidth="1" min="19" max="19"/>
     <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="10" customWidth="1" min="21" max="21"/>
+    <col width="6" customWidth="1" min="22" max="22"/>
+    <col width="10" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -547,6 +550,21 @@
           <t>EncoderTrain</t>
         </is>
       </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>HeadMode</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>PBRU</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>DecoderDim</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2827,193 +2845,541 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>TAR-DCR</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr"/>
+          <t>Run7</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>C0_Bilinear_D158</t>
+        </is>
+      </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E39" s="2" t="n">
-        <v>98.69</v>
+        <v>91.16</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>98.89</v>
+        <v>91.64</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>99.7</v>
+        <v>99.13</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>98.79000000000001</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>97.61</v>
+        <v>84.16</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>98.62</v>
+        <v>90.94</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>36.081</v>
-      </c>
-      <c r="L39" s="2" t="n"/>
+        <v>29.542</v>
+      </c>
+      <c r="L39" s="2" t="n">
+        <v>27.428</v>
+      </c>
       <c r="M39" s="2" t="n">
-        <v>36.081</v>
+        <v>28.814</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>16.2593</v>
-      </c>
-      <c r="O39" s="3" t="n"/>
+        <v>12.5866</v>
+      </c>
+      <c r="O39" s="3" t="n">
+        <v>1.431e-05</v>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>high2</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>last2</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>bilinear</t>
+        </is>
+      </c>
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" t="n">
+        <v>158</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>TAR-DCR</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr"/>
+          <t>Run7</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>C0_Bilinear_D158</t>
+        </is>
+      </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E40" s="2" t="n">
-        <v>91.20999999999999</v>
+        <v>94.23999999999999</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>93.03</v>
+        <v>96.20999999999999</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>99.2</v>
+        <v>99.62</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>92.11</v>
+        <v>95.22</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>85.37</v>
+        <v>90.87</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>91.69</v>
+        <v>95.02</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>36.081</v>
-      </c>
-      <c r="L40" s="2" t="n"/>
+        <v>29.542</v>
+      </c>
+      <c r="L40" s="2" t="n">
+        <v>27.428</v>
+      </c>
       <c r="M40" s="2" t="n">
-        <v>36.081</v>
+        <v>28.814</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>16.2593</v>
-      </c>
-      <c r="O40" s="3" t="n"/>
+        <v>12.5866</v>
+      </c>
+      <c r="O40" s="3" t="n">
+        <v>1.049e-05</v>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>high2</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>last2</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>bilinear</t>
+        </is>
+      </c>
+      <c r="V40" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" t="n">
+        <v>158</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>TAR-DCR</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr"/>
+          <t>Run7</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>M1_PBRU_D158</t>
+        </is>
+      </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E41" s="2" t="n">
-        <v>79.73</v>
+        <v>90.39</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>86.51000000000001</v>
+        <v>92.87</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>92.29000000000001</v>
+        <v>99.16</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>82.98999999999999</v>
+        <v>91.61</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>70.92</v>
+        <v>84.52</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>78.01000000000001</v>
+        <v>91.17</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>36.081</v>
-      </c>
-      <c r="L41" s="2" t="n"/>
+        <v>29.548</v>
+      </c>
+      <c r="L41" s="2" t="n">
+        <v>27.434</v>
+      </c>
       <c r="M41" s="2" t="n">
-        <v>36.081</v>
+        <v>28.819</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>16.2593</v>
-      </c>
-      <c r="O41" s="3" t="n"/>
+        <v>12.6055</v>
+      </c>
+      <c r="O41" s="3" t="n">
+        <v>1.431e-05</v>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>high2</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>last2</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>pixelshuffle</t>
+        </is>
+      </c>
+      <c r="V41" t="n">
+        <v>1</v>
+      </c>
+      <c r="W41" t="n">
+        <v>158</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>TAR-DCR</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr"/>
+          <t>Run7</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>M1_PBRU_D158</t>
+        </is>
+      </c>
       <c r="D42" t="inlineStr">
         <is>
           <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E42" s="2" t="n">
-        <v>93.28</v>
+        <v>93.78</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>96.79000000000001</v>
+        <v>96.38</v>
       </c>
       <c r="G42" s="2" t="n">
         <v>99.61</v>
       </c>
       <c r="H42" s="2" t="n">
+        <v>95.06</v>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>90.59</v>
+      </c>
+      <c r="J42" s="2" t="n">
+        <v>94.86</v>
+      </c>
+      <c r="K42" s="2" t="n">
+        <v>29.548</v>
+      </c>
+      <c r="L42" s="2" t="n">
+        <v>27.434</v>
+      </c>
+      <c r="M42" s="2" t="n">
+        <v>28.819</v>
+      </c>
+      <c r="N42" s="2" t="n">
+        <v>12.6055</v>
+      </c>
+      <c r="O42" s="3" t="n">
+        <v>1.526e-05</v>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>high2</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>last2</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>pixelshuffle</t>
+        </is>
+      </c>
+      <c r="V42" t="n">
+        <v>1</v>
+      </c>
+      <c r="W42" t="n">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>CDD-CD-256</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>98.69</v>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>98.89</v>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>98.79000000000001</v>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>97.61</v>
+      </c>
+      <c r="J43" s="2" t="n">
+        <v>98.62</v>
+      </c>
+      <c r="K43" s="2" t="n">
+        <v>36.081</v>
+      </c>
+      <c r="L43" s="2" t="n"/>
+      <c r="M43" s="2" t="n">
+        <v>36.081</v>
+      </c>
+      <c r="N43" s="2" t="n">
+        <v>16.2593</v>
+      </c>
+      <c r="O43" s="3" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LEVIR-CD-256</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>91.20999999999999</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>93.03</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>92.11</v>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>85.37</v>
+      </c>
+      <c r="J44" s="2" t="n">
+        <v>91.69</v>
+      </c>
+      <c r="K44" s="2" t="n">
+        <v>36.081</v>
+      </c>
+      <c r="L44" s="2" t="n"/>
+      <c r="M44" s="2" t="n">
+        <v>36.081</v>
+      </c>
+      <c r="N44" s="2" t="n">
+        <v>16.2593</v>
+      </c>
+      <c r="O44" s="3" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>79.73</v>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>86.51000000000001</v>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>92.29000000000001</v>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>82.98999999999999</v>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>70.92</v>
+      </c>
+      <c r="J45" s="2" t="n">
+        <v>78.01000000000001</v>
+      </c>
+      <c r="K45" s="2" t="n">
+        <v>36.081</v>
+      </c>
+      <c r="L45" s="2" t="n"/>
+      <c r="M45" s="2" t="n">
+        <v>36.081</v>
+      </c>
+      <c r="N45" s="2" t="n">
+        <v>16.2593</v>
+      </c>
+      <c r="O45" s="3" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>WHU-CD-256</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>93.28</v>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>96.79000000000001</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>99.61</v>
+      </c>
+      <c r="H46" s="2" t="n">
         <v>95</v>
       </c>
-      <c r="I42" s="2" t="n">
+      <c r="I46" s="2" t="n">
         <v>90.47</v>
       </c>
-      <c r="J42" s="2" t="n">
+      <c r="J46" s="2" t="n">
         <v>94.8</v>
       </c>
-      <c r="K42" s="2" t="n">
+      <c r="K46" s="2" t="n">
         <v>36.081</v>
       </c>
-      <c r="L42" s="2" t="n"/>
-      <c r="M42" s="2" t="n">
+      <c r="L46" s="2" t="n"/>
+      <c r="M46" s="2" t="n">
         <v>36.081</v>
       </c>
-      <c r="N42" s="2" t="n">
+      <c r="N46" s="2" t="n">
         <v>16.2593</v>
       </c>
-      <c r="O42" s="3" t="n"/>
+      <c r="O46" s="3" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T42"/>
+  <autoFilter ref="A1:W46"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/experiment_metrics.xlsx
+++ b/docs/experiment_metrics.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="metrics" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'metrics'!$A$1:$W$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'metrics'!$A$1:$W$48</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W46"/>
+  <dimension ref="A1:W48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>M1_PBRU_D158</t>
+          <t>C1_PixelShuffle_D158</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3038,28 +3038,28 @@
         </is>
       </c>
       <c r="E41" s="2" t="n">
-        <v>90.39</v>
+        <v>90.81999999999999</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>92.87</v>
+        <v>92.23999999999999</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>99.16</v>
+        <v>99.14</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>91.61</v>
+        <v>91.52</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>84.52</v>
+        <v>84.37</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>91.17</v>
+        <v>91.06999999999999</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>29.548</v>
+        <v>29.547</v>
       </c>
       <c r="L41" s="2" t="n">
-        <v>27.434</v>
+        <v>27.433</v>
       </c>
       <c r="M41" s="2" t="n">
         <v>28.819</v>
@@ -3068,7 +3068,7 @@
         <v>12.6055</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>1.431e-05</v>
+        <v>1.669e-05</v>
       </c>
       <c r="P41" t="inlineStr">
         <is>
@@ -3097,7 +3097,7 @@
         </is>
       </c>
       <c r="V41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
         <v>158</v>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>M1_PBRU_D158</t>
+          <t>C1_PixelShuffle_D158</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3125,28 +3125,28 @@
         </is>
       </c>
       <c r="E42" s="2" t="n">
-        <v>93.78</v>
+        <v>93.81999999999999</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>96.38</v>
+        <v>95.94</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>99.61</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>95.06</v>
+        <v>94.87</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>90.59</v>
+        <v>90.23999999999999</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>94.86</v>
+        <v>94.66</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>29.548</v>
+        <v>29.547</v>
       </c>
       <c r="L42" s="2" t="n">
-        <v>27.434</v>
+        <v>27.433</v>
       </c>
       <c r="M42" s="2" t="n">
         <v>28.819</v>
@@ -3155,7 +3155,7 @@
         <v>12.6055</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>1.526e-05</v>
+        <v>1.431e-05</v>
       </c>
       <c r="P42" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         </is>
       </c>
       <c r="V42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
         <v>158</v>
@@ -3193,96 +3193,176 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>TAR-DCR</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr"/>
+          <t>Run7</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>M1_PBRU_D158</t>
+        </is>
+      </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E43" s="2" t="n">
-        <v>98.69</v>
+        <v>90.39</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>98.89</v>
+        <v>92.87</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>99.7</v>
+        <v>99.16</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>98.79000000000001</v>
+        <v>91.61</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>97.61</v>
+        <v>84.52</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>98.62</v>
+        <v>91.17</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>36.081</v>
-      </c>
-      <c r="L43" s="2" t="n"/>
+        <v>29.548</v>
+      </c>
+      <c r="L43" s="2" t="n">
+        <v>27.434</v>
+      </c>
       <c r="M43" s="2" t="n">
-        <v>36.081</v>
+        <v>28.819</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>16.2593</v>
-      </c>
-      <c r="O43" s="3" t="n"/>
+        <v>12.6055</v>
+      </c>
+      <c r="O43" s="3" t="n">
+        <v>1.431e-05</v>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>high2</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>last2</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>pixelshuffle</t>
+        </is>
+      </c>
+      <c r="V43" t="n">
+        <v>1</v>
+      </c>
+      <c r="W43" t="n">
+        <v>158</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>TAR-DCR</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr"/>
+          <t>Run7</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>M1_PBRU_D158</t>
+        </is>
+      </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E44" s="2" t="n">
-        <v>91.20999999999999</v>
+        <v>93.78</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>93.03</v>
+        <v>96.38</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>99.2</v>
+        <v>99.61</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>92.11</v>
+        <v>95.06</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>85.37</v>
+        <v>90.59</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>91.69</v>
+        <v>94.86</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>36.081</v>
-      </c>
-      <c r="L44" s="2" t="n"/>
+        <v>29.548</v>
+      </c>
+      <c r="L44" s="2" t="n">
+        <v>27.434</v>
+      </c>
       <c r="M44" s="2" t="n">
-        <v>36.081</v>
+        <v>28.819</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>16.2593</v>
-      </c>
-      <c r="O44" s="3" t="n"/>
+        <v>12.6055</v>
+      </c>
+      <c r="O44" s="3" t="n">
+        <v>1.526e-05</v>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>high2</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>last2</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>pixelshuffle</t>
+        </is>
+      </c>
+      <c r="V44" t="n">
+        <v>1</v>
+      </c>
+      <c r="W44" t="n">
+        <v>158</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3298,26 +3378,26 @@
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E45" s="2" t="n">
-        <v>79.73</v>
+        <v>98.69</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>86.51000000000001</v>
+        <v>98.89</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>92.29000000000001</v>
+        <v>99.7</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>82.98999999999999</v>
+        <v>98.79000000000001</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>70.92</v>
+        <v>97.61</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>78.01000000000001</v>
+        <v>98.62</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>36.081</v>
@@ -3345,26 +3425,26 @@
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E46" s="2" t="n">
-        <v>93.28</v>
+        <v>91.20999999999999</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>96.79000000000001</v>
+        <v>93.03</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>99.61</v>
+        <v>99.2</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>95</v>
+        <v>92.11</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>90.47</v>
+        <v>85.37</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>94.8</v>
+        <v>91.69</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>36.081</v>
@@ -3378,8 +3458,102 @@
       </c>
       <c r="O46" s="3" t="n"/>
     </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>79.73</v>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v>86.51000000000001</v>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>92.29000000000001</v>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>82.98999999999999</v>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>70.92</v>
+      </c>
+      <c r="J47" s="2" t="n">
+        <v>78.01000000000001</v>
+      </c>
+      <c r="K47" s="2" t="n">
+        <v>36.081</v>
+      </c>
+      <c r="L47" s="2" t="n"/>
+      <c r="M47" s="2" t="n">
+        <v>36.081</v>
+      </c>
+      <c r="N47" s="2" t="n">
+        <v>16.2593</v>
+      </c>
+      <c r="O47" s="3" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>WHU-CD-256</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>93.28</v>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>96.79000000000001</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>99.61</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>90.47</v>
+      </c>
+      <c r="J48" s="2" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="K48" s="2" t="n">
+        <v>36.081</v>
+      </c>
+      <c r="L48" s="2" t="n"/>
+      <c r="M48" s="2" t="n">
+        <v>36.081</v>
+      </c>
+      <c r="N48" s="2" t="n">
+        <v>16.2593</v>
+      </c>
+      <c r="O48" s="3" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:W46"/>
+  <autoFilter ref="A1:W48"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/experiment_metrics.xlsx
+++ b/docs/experiment_metrics.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="metrics" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'metrics'!$A$1:$W$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'metrics'!$A$1:$Y$52</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W48"/>
+  <dimension ref="A1:Y52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -447,6 +447,8 @@
     <col width="10" customWidth="1" min="21" max="21"/>
     <col width="6" customWidth="1" min="22" max="22"/>
     <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="6" customWidth="1" min="24" max="24"/>
+    <col width="10" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -565,6 +567,16 @@
           <t>DecoderDim</t>
         </is>
       </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>MPCR</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>MPCRMode</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3367,166 +3379,314 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>TAR-DCR</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr"/>
+          <t>Run8</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>C0_MPCR_Same2</t>
+        </is>
+      </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E45" s="2" t="n">
-        <v>98.69</v>
+        <v>90.67</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>98.89</v>
+        <v>92.04000000000001</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>99.7</v>
+        <v>99.13</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>98.79000000000001</v>
+        <v>91.34999999999999</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>97.61</v>
+        <v>84.08</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>98.62</v>
+        <v>90.89</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>36.081</v>
-      </c>
-      <c r="L45" s="2" t="n"/>
+        <v>29.584</v>
+      </c>
+      <c r="L45" s="2" t="n">
+        <v>27.47</v>
+      </c>
       <c r="M45" s="2" t="n">
-        <v>36.081</v>
+        <v>28.829</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>16.2593</v>
-      </c>
-      <c r="O45" s="3" t="n"/>
+        <v>12.6062</v>
+      </c>
+      <c r="O45" s="3" t="n">
+        <v>1.431e-05</v>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>high2</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>last2</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>bilinear</t>
+        </is>
+      </c>
+      <c r="V45" t="n">
+        <v>0</v>
+      </c>
+      <c r="W45" t="n">
+        <v>160</v>
+      </c>
+      <c r="X45" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>same2</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>TAR-DCR</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr"/>
+          <t>Run8</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>C0_MPCR_Same2</t>
+        </is>
+      </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E46" s="2" t="n">
-        <v>91.20999999999999</v>
+        <v>93.7</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>93.03</v>
+        <v>96.75</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>99.2</v>
+        <v>99.62</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>92.11</v>
+        <v>95.2</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>85.37</v>
+        <v>90.84</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>91.69</v>
+        <v>95</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>36.081</v>
-      </c>
-      <c r="L46" s="2" t="n"/>
+        <v>29.584</v>
+      </c>
+      <c r="L46" s="2" t="n">
+        <v>27.47</v>
+      </c>
       <c r="M46" s="2" t="n">
-        <v>36.081</v>
+        <v>28.829</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>16.2593</v>
-      </c>
-      <c r="O46" s="3" t="n"/>
+        <v>12.6062</v>
+      </c>
+      <c r="O46" s="3" t="n">
+        <v>1.049e-05</v>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>high2</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>last2</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>bilinear</t>
+        </is>
+      </c>
+      <c r="V46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W46" t="n">
+        <v>160</v>
+      </c>
+      <c r="X46" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>same2</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>TAR-DCR</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
+          <t>Run8</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>M1_MPCR_Multi2</t>
+        </is>
+      </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E47" s="2" t="n">
-        <v>79.73</v>
+        <v>89.72</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>86.51000000000001</v>
+        <v>92.91</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>92.29000000000001</v>
+        <v>99.13</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>82.98999999999999</v>
+        <v>91.29000000000001</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>70.92</v>
+        <v>83.97</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>78.01000000000001</v>
+        <v>90.83</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>36.081</v>
-      </c>
-      <c r="L47" s="2" t="n"/>
+        <v>29.584</v>
+      </c>
+      <c r="L47" s="2" t="n">
+        <v>27.47</v>
+      </c>
       <c r="M47" s="2" t="n">
-        <v>36.081</v>
+        <v>28.829</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>16.2593</v>
-      </c>
-      <c r="O47" s="3" t="n"/>
+        <v>12.6062</v>
+      </c>
+      <c r="O47" s="3" t="n">
+        <v>1.144e-05</v>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>high2</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>last2</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>bilinear</t>
+        </is>
+      </c>
+      <c r="V47" t="n">
+        <v>0</v>
+      </c>
+      <c r="W47" t="n">
+        <v>160</v>
+      </c>
+      <c r="X47" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>multi2</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>TAR-DCR</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr"/>
+          <t>Run8</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>M1_MPCR_Multi2</t>
+        </is>
+      </c>
       <c r="D48" t="inlineStr">
         <is>
           <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E48" s="2" t="n">
-        <v>93.28</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>96.79000000000001</v>
+        <v>96.12</v>
       </c>
       <c r="G48" s="2" t="n">
         <v>99.61</v>
@@ -3538,22 +3698,254 @@
         <v>90.47</v>
       </c>
       <c r="J48" s="2" t="n">
+        <v>94.79000000000001</v>
+      </c>
+      <c r="K48" s="2" t="n">
+        <v>29.584</v>
+      </c>
+      <c r="L48" s="2" t="n">
+        <v>27.47</v>
+      </c>
+      <c r="M48" s="2" t="n">
+        <v>28.829</v>
+      </c>
+      <c r="N48" s="2" t="n">
+        <v>12.6062</v>
+      </c>
+      <c r="O48" s="3" t="n">
+        <v>1.24e-05</v>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>high2</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>last2</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>bilinear</t>
+        </is>
+      </c>
+      <c r="V48" t="n">
+        <v>0</v>
+      </c>
+      <c r="W48" t="n">
+        <v>160</v>
+      </c>
+      <c r="X48" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>multi2</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>CDD-CD-256</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="n">
+        <v>98.69</v>
+      </c>
+      <c r="F49" s="2" t="n">
+        <v>98.89</v>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>98.79000000000001</v>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>97.61</v>
+      </c>
+      <c r="J49" s="2" t="n">
+        <v>98.62</v>
+      </c>
+      <c r="K49" s="2" t="n">
+        <v>36.081</v>
+      </c>
+      <c r="L49" s="2" t="n"/>
+      <c r="M49" s="2" t="n">
+        <v>36.081</v>
+      </c>
+      <c r="N49" s="2" t="n">
+        <v>16.2593</v>
+      </c>
+      <c r="O49" s="3" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LEVIR-CD-256</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="n">
+        <v>91.20999999999999</v>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>93.03</v>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>92.11</v>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>85.37</v>
+      </c>
+      <c r="J50" s="2" t="n">
+        <v>91.69</v>
+      </c>
+      <c r="K50" s="2" t="n">
+        <v>36.081</v>
+      </c>
+      <c r="L50" s="2" t="n"/>
+      <c r="M50" s="2" t="n">
+        <v>36.081</v>
+      </c>
+      <c r="N50" s="2" t="n">
+        <v>16.2593</v>
+      </c>
+      <c r="O50" s="3" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="n">
+        <v>79.73</v>
+      </c>
+      <c r="F51" s="2" t="n">
+        <v>86.51000000000001</v>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>92.29000000000001</v>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>82.98999999999999</v>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>70.92</v>
+      </c>
+      <c r="J51" s="2" t="n">
+        <v>78.01000000000001</v>
+      </c>
+      <c r="K51" s="2" t="n">
+        <v>36.081</v>
+      </c>
+      <c r="L51" s="2" t="n"/>
+      <c r="M51" s="2" t="n">
+        <v>36.081</v>
+      </c>
+      <c r="N51" s="2" t="n">
+        <v>16.2593</v>
+      </c>
+      <c r="O51" s="3" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>WHU-CD-256</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="n">
+        <v>93.28</v>
+      </c>
+      <c r="F52" s="2" t="n">
+        <v>96.79000000000001</v>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>99.61</v>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>90.47</v>
+      </c>
+      <c r="J52" s="2" t="n">
         <v>94.8</v>
       </c>
-      <c r="K48" s="2" t="n">
+      <c r="K52" s="2" t="n">
         <v>36.081</v>
       </c>
-      <c r="L48" s="2" t="n"/>
-      <c r="M48" s="2" t="n">
+      <c r="L52" s="2" t="n"/>
+      <c r="M52" s="2" t="n">
         <v>36.081</v>
       </c>
-      <c r="N48" s="2" t="n">
+      <c r="N52" s="2" t="n">
         <v>16.2593</v>
       </c>
-      <c r="O48" s="3" t="n"/>
+      <c r="O52" s="3" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W48"/>
+  <autoFilter ref="A1:Y52"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/experiment_metrics.xlsx
+++ b/docs/experiment_metrics.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="metrics" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'metrics'!$A$1:$Y$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'metrics'!$A$1:$Y$56</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y52"/>
+  <dimension ref="A1:Y56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3759,193 +3759,573 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>TAR-DCR</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr"/>
+          <t>Run9</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>C0_FTR_Post</t>
+        </is>
+      </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E49" s="2" t="n">
-        <v>98.69</v>
+        <v>90.42</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>98.89</v>
+        <v>92.43000000000001</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>99.7</v>
+        <v>99.13</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>98.79000000000001</v>
+        <v>91.42</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>97.61</v>
+        <v>84.19</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>98.62</v>
+        <v>90.95999999999999</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>36.081</v>
-      </c>
-      <c r="L49" s="2" t="n"/>
+        <v>29.718</v>
+      </c>
+      <c r="L49" s="2" t="n">
+        <v>27.604</v>
+      </c>
       <c r="M49" s="2" t="n">
-        <v>36.081</v>
+        <v>28.829</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>16.2593</v>
-      </c>
-      <c r="O49" s="3" t="n"/>
+        <v>12.6062</v>
+      </c>
+      <c r="O49" s="3" t="n">
+        <v>1.907e-05</v>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>high2</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>last2</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>bilinear</t>
+        </is>
+      </c>
+      <c r="V49" t="n">
+        <v>0</v>
+      </c>
+      <c r="W49" t="n">
+        <v>160</v>
+      </c>
+      <c r="X49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>multi2</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>TAR-DCR</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr"/>
+          <t>Run9</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>C0_FTR_Post</t>
+        </is>
+      </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E50" s="2" t="n">
-        <v>91.20999999999999</v>
+        <v>93.94</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>93.03</v>
+        <v>96.01000000000001</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>99.2</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>92.11</v>
+        <v>94.95999999999999</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>85.37</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>91.69</v>
+        <v>94.75</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>36.081</v>
-      </c>
-      <c r="L50" s="2" t="n"/>
+        <v>29.718</v>
+      </c>
+      <c r="L50" s="2" t="n">
+        <v>27.604</v>
+      </c>
       <c r="M50" s="2" t="n">
-        <v>36.081</v>
+        <v>28.829</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>16.2593</v>
-      </c>
-      <c r="O50" s="3" t="n"/>
+        <v>12.6062</v>
+      </c>
+      <c r="O50" s="3" t="n">
+        <v>6.199e-06</v>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>high2</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>last2</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>bilinear</t>
+        </is>
+      </c>
+      <c r="V50" t="n">
+        <v>0</v>
+      </c>
+      <c r="W50" t="n">
+        <v>160</v>
+      </c>
+      <c r="X50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>multi2</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>TAR-DCR</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr"/>
+          <t>Run9</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>M1_BiFTR</t>
+        </is>
+      </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E51" s="2" t="n">
-        <v>79.73</v>
+        <v>90.37</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>86.51000000000001</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>92.29000000000001</v>
+        <v>99.14</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>82.98999999999999</v>
+        <v>91.47</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>70.92</v>
+        <v>84.28</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>78.01000000000001</v>
+        <v>91.02</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>36.081</v>
-      </c>
-      <c r="L51" s="2" t="n"/>
+        <v>29.755</v>
+      </c>
+      <c r="L51" s="2" t="n">
+        <v>27.641</v>
+      </c>
       <c r="M51" s="2" t="n">
-        <v>36.081</v>
+        <v>28.829</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>16.2593</v>
-      </c>
-      <c r="O51" s="3" t="n"/>
+        <v>12.6062</v>
+      </c>
+      <c r="O51" s="3" t="n">
+        <v>2.384e-05</v>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>high2</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>last2</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>bilinear</t>
+        </is>
+      </c>
+      <c r="V51" t="n">
+        <v>0</v>
+      </c>
+      <c r="W51" t="n">
+        <v>160</v>
+      </c>
+      <c r="X51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>multi2</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>TAR-DCR</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr"/>
+          <t>Run9</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>M1_BiFTR</t>
+        </is>
+      </c>
       <c r="D52" t="inlineStr">
         <is>
           <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E52" s="2" t="n">
-        <v>93.28</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>96.79000000000001</v>
+        <v>96.25</v>
       </c>
       <c r="G52" s="2" t="n">
         <v>99.61</v>
       </c>
       <c r="H52" s="2" t="n">
+        <v>95.06</v>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>90.59</v>
+      </c>
+      <c r="J52" s="2" t="n">
+        <v>94.86</v>
+      </c>
+      <c r="K52" s="2" t="n">
+        <v>29.755</v>
+      </c>
+      <c r="L52" s="2" t="n">
+        <v>27.641</v>
+      </c>
+      <c r="M52" s="2" t="n">
+        <v>28.829</v>
+      </c>
+      <c r="N52" s="2" t="n">
+        <v>12.6062</v>
+      </c>
+      <c r="O52" s="3" t="n">
+        <v>1.144e-05</v>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>high2</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>last2</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>bilinear</t>
+        </is>
+      </c>
+      <c r="V52" t="n">
+        <v>0</v>
+      </c>
+      <c r="W52" t="n">
+        <v>160</v>
+      </c>
+      <c r="X52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>multi2</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>CDD-CD-256</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="n">
+        <v>98.69</v>
+      </c>
+      <c r="F53" s="2" t="n">
+        <v>98.89</v>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="H53" s="2" t="n">
+        <v>98.79000000000001</v>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>97.61</v>
+      </c>
+      <c r="J53" s="2" t="n">
+        <v>98.62</v>
+      </c>
+      <c r="K53" s="2" t="n">
+        <v>36.081</v>
+      </c>
+      <c r="L53" s="2" t="n"/>
+      <c r="M53" s="2" t="n">
+        <v>36.081</v>
+      </c>
+      <c r="N53" s="2" t="n">
+        <v>16.2593</v>
+      </c>
+      <c r="O53" s="3" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LEVIR-CD-256</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="n">
+        <v>91.20999999999999</v>
+      </c>
+      <c r="F54" s="2" t="n">
+        <v>93.03</v>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>92.11</v>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>85.37</v>
+      </c>
+      <c r="J54" s="2" t="n">
+        <v>91.69</v>
+      </c>
+      <c r="K54" s="2" t="n">
+        <v>36.081</v>
+      </c>
+      <c r="L54" s="2" t="n"/>
+      <c r="M54" s="2" t="n">
+        <v>36.081</v>
+      </c>
+      <c r="N54" s="2" t="n">
+        <v>16.2593</v>
+      </c>
+      <c r="O54" s="3" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="n">
+        <v>79.73</v>
+      </c>
+      <c r="F55" s="2" t="n">
+        <v>86.51000000000001</v>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>92.29000000000001</v>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>82.98999999999999</v>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>70.92</v>
+      </c>
+      <c r="J55" s="2" t="n">
+        <v>78.01000000000001</v>
+      </c>
+      <c r="K55" s="2" t="n">
+        <v>36.081</v>
+      </c>
+      <c r="L55" s="2" t="n"/>
+      <c r="M55" s="2" t="n">
+        <v>36.081</v>
+      </c>
+      <c r="N55" s="2" t="n">
+        <v>16.2593</v>
+      </c>
+      <c r="O55" s="3" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>WHU-CD-256</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="n">
+        <v>93.28</v>
+      </c>
+      <c r="F56" s="2" t="n">
+        <v>96.79000000000001</v>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>99.61</v>
+      </c>
+      <c r="H56" s="2" t="n">
         <v>95</v>
       </c>
-      <c r="I52" s="2" t="n">
+      <c r="I56" s="2" t="n">
         <v>90.47</v>
       </c>
-      <c r="J52" s="2" t="n">
+      <c r="J56" s="2" t="n">
         <v>94.8</v>
       </c>
-      <c r="K52" s="2" t="n">
+      <c r="K56" s="2" t="n">
         <v>36.081</v>
       </c>
-      <c r="L52" s="2" t="n"/>
-      <c r="M52" s="2" t="n">
+      <c r="L56" s="2" t="n"/>
+      <c r="M56" s="2" t="n">
         <v>36.081</v>
       </c>
-      <c r="N52" s="2" t="n">
+      <c r="N56" s="2" t="n">
         <v>16.2593</v>
       </c>
-      <c r="O52" s="3" t="n"/>
+      <c r="O56" s="3" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Y52"/>
+  <autoFilter ref="A1:Y56"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/experiment_metrics.xlsx
+++ b/docs/experiment_metrics.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="metrics" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'metrics'!$A$1:$Y$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'metrics'!$A$1:$Y$58</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y56"/>
+  <dimension ref="A1:Y58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -586,55 +586,90 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run10</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>A0_Plain</t>
+          <t>C0_PlainPF_DW5</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>97.13</v>
+        <v>90.81</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>97.52</v>
+        <v>92.06</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>99.34</v>
+        <v>99.13</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>97.31999999999999</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>94.79000000000001</v>
+        <v>84.22</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>96.95</v>
+        <v>90.98</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>28.832</v>
+        <v>29.546</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0.838</v>
+        <v>27.432</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>28.829</v>
+        <v>28.818</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>12.6062</v>
+        <v>12.6028</v>
       </c>
       <c r="O2" s="3" t="n">
-        <v>2.241e-05</v>
+        <v>2.67e-05</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>plain</t>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>high2</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>last2</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>bilinear</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>158</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>multi2</t>
         </is>
       </c>
     </row>
@@ -646,12 +681,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Run1</t>
+          <t>Run10</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>A0_Plain</t>
+          <t>M1_PFDR_DW5</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -660,41 +695,76 @@
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>88.98</v>
+        <v>90.11</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>91.23</v>
+        <v>92.8</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>99</v>
+        <v>99.14</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>90.09</v>
+        <v>91.44</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>81.97</v>
+        <v>84.22</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>89.56999999999999</v>
+        <v>90.98</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>28.832</v>
+        <v>29.55</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0.838</v>
+        <v>27.436</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>28.829</v>
+        <v>28.818</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>12.6062</v>
+        <v>12.6028</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>2.098e-05</v>
+        <v>1.526e-05</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>plain</t>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>high2</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>last2</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>bilinear</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>158</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>multi2</t>
         </is>
       </c>
     </row>
@@ -716,26 +786,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>77.09999999999999</v>
+        <v>97.13</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>85.63</v>
+        <v>97.52</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>91.55</v>
+        <v>99.34</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>81.14</v>
+        <v>97.31999999999999</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>68.26000000000001</v>
+        <v>94.79000000000001</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>75.70999999999999</v>
+        <v>96.95</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>28.832</v>
@@ -750,7 +820,7 @@
         <v>12.6062</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>1.335e-05</v>
+        <v>2.241e-05</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -776,26 +846,26 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>91.81999999999999</v>
+        <v>88.98</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>95.34999999999999</v>
+        <v>91.23</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>99.5</v>
+        <v>99</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>93.55</v>
+        <v>90.09</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>87.88</v>
+        <v>81.97</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>93.29000000000001</v>
+        <v>89.56999999999999</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>28.832</v>
@@ -810,7 +880,7 @@
         <v>12.6062</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>1.049e-05</v>
+        <v>2.098e-05</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -831,37 +901,37 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>A1_TAR</t>
+          <t>A0_Plain</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>97.37</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>97.33</v>
+        <v>85.63</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>99.34</v>
+        <v>91.55</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>97.34999999999999</v>
+        <v>81.14</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>94.83</v>
+        <v>68.26000000000001</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>96.97</v>
+        <v>75.70999999999999</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>29.293</v>
+        <v>28.832</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>1.299</v>
+        <v>0.838</v>
       </c>
       <c r="M6" s="2" t="n">
         <v>28.829</v>
@@ -870,11 +940,11 @@
         <v>12.6062</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>1.574e-05</v>
+        <v>1.335e-05</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>tar</t>
+          <t>plain</t>
         </is>
       </c>
     </row>
@@ -891,37 +961,37 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>A1_TAR</t>
+          <t>A0_Plain</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>88.88</v>
+        <v>91.81999999999999</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>91.20999999999999</v>
+        <v>95.34999999999999</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>99</v>
+        <v>99.5</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>90.03</v>
+        <v>93.55</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>81.87</v>
+        <v>87.88</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>89.5</v>
+        <v>93.29000000000001</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>29.293</v>
+        <v>28.832</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>1.299</v>
+        <v>0.838</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>28.829</v>
@@ -930,11 +1000,11 @@
         <v>12.6062</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>1.001e-05</v>
+        <v>1.049e-05</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>tar</t>
+          <t>plain</t>
         </is>
       </c>
     </row>
@@ -956,26 +1026,26 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>75.62</v>
+        <v>97.37</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>86.23999999999999</v>
+        <v>97.33</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>91.41</v>
+        <v>99.34</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>80.58</v>
+        <v>97.34999999999999</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>67.48</v>
+        <v>94.83</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>75.09999999999999</v>
+        <v>96.97</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>29.293</v>
@@ -990,7 +1060,7 @@
         <v>12.6062</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>2.003e-05</v>
+        <v>1.574e-05</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -1016,26 +1086,26 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>92.38</v>
+        <v>88.88</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>95.43000000000001</v>
+        <v>91.20999999999999</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>99.52</v>
+        <v>99</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>93.88</v>
+        <v>90.03</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>88.47</v>
+        <v>81.87</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>93.63</v>
+        <v>89.5</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>29.293</v>
@@ -1050,7 +1120,7 @@
         <v>12.6062</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>1.144e-05</v>
+        <v>1.001e-05</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
@@ -1071,37 +1141,37 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>A2_Full</t>
+          <t>A1_TAR</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>97.65000000000001</v>
+        <v>75.62</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>97.70999999999999</v>
+        <v>86.23999999999999</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>99.43000000000001</v>
+        <v>91.41</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>97.68000000000001</v>
+        <v>80.58</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>95.47</v>
+        <v>67.48</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>97.34999999999999</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>29.558</v>
+        <v>29.293</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>1.564</v>
+        <v>1.299</v>
       </c>
       <c r="M10" s="2" t="n">
         <v>28.829</v>
@@ -1110,11 +1180,11 @@
         <v>12.6062</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>5.722e-05</v>
+        <v>2.003e-05</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>tar</t>
         </is>
       </c>
     </row>
@@ -1131,37 +1201,37 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>A2_Full</t>
+          <t>A1_TAR</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>88.76000000000001</v>
+        <v>92.38</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>91.95999999999999</v>
+        <v>95.43000000000001</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>99.03</v>
+        <v>99.52</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>90.33</v>
+        <v>93.88</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>82.37</v>
+        <v>88.47</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>89.81999999999999</v>
+        <v>93.63</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>29.558</v>
+        <v>29.293</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>1.564</v>
+        <v>1.299</v>
       </c>
       <c r="M11" s="2" t="n">
         <v>28.829</v>
@@ -1170,11 +1240,11 @@
         <v>12.6062</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>0.0001106</v>
+        <v>1.144e-05</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>tar</t>
         </is>
       </c>
     </row>
@@ -1196,26 +1266,26 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>76.2</v>
+        <v>97.65000000000001</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>87</v>
+        <v>97.70999999999999</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>91.7</v>
+        <v>99.43000000000001</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>81.23999999999999</v>
+        <v>97.68000000000001</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>68.41</v>
+        <v>95.47</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>75.94</v>
+        <v>97.34999999999999</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>29.558</v>
@@ -1230,7 +1300,7 @@
         <v>12.6062</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>1.626e-05</v>
+        <v>5.722e-05</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
@@ -1256,26 +1326,26 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>92.09</v>
+        <v>88.76000000000001</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>96.06999999999999</v>
+        <v>91.95999999999999</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>99.54000000000001</v>
+        <v>99.03</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>94.03</v>
+        <v>90.33</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>88.73999999999999</v>
+        <v>82.37</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>93.79000000000001</v>
+        <v>89.81999999999999</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>29.558</v>
@@ -1290,7 +1360,7 @@
         <v>12.6062</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>6.199e-06</v>
+        <v>0.0001106</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
@@ -1306,42 +1376,42 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>dcr_frozen</t>
+          <t>A2_Full</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>89.53</v>
+        <v>76.2</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>92.31</v>
+        <v>87</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>99.09</v>
+        <v>91.7</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>90.90000000000001</v>
+        <v>81.23999999999999</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>83.31</v>
+        <v>68.41</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>90.41</v>
+        <v>75.94</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>29.107</v>
+        <v>29.558</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>1.113</v>
+        <v>1.564</v>
       </c>
       <c r="M14" s="2" t="n">
         <v>28.829</v>
@@ -1350,11 +1420,11 @@
         <v>12.6062</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>2.48e-05</v>
+        <v>1.626e-05</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>dcr</t>
+          <t>full</t>
         </is>
       </c>
     </row>
@@ -1366,42 +1436,42 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Run2</t>
+          <t>Run1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>dcr_frozen</t>
+          <t>A2_Full</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>77.23</v>
+        <v>92.09</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>87.41</v>
+        <v>96.06999999999999</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>92.01000000000001</v>
+        <v>99.54000000000001</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>82.01000000000001</v>
+        <v>94.03</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>69.5</v>
+        <v>88.73999999999999</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>76.90000000000001</v>
+        <v>93.79000000000001</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>29.107</v>
+        <v>29.558</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>1.113</v>
+        <v>1.564</v>
       </c>
       <c r="M15" s="2" t="n">
         <v>28.829</v>
@@ -1410,11 +1480,11 @@
         <v>12.6062</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>2.563e-05</v>
+        <v>6.199e-06</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>dcr</t>
+          <t>full</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1501,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>full_frozen</t>
+          <t>dcr_frozen</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1440,28 +1510,28 @@
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>89.98</v>
+        <v>89.53</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>91.91</v>
+        <v>92.31</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>99.09</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>90.94</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>83.38</v>
+        <v>83.31</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>90.45</v>
+        <v>90.41</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>29.57</v>
+        <v>29.107</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>1.576</v>
+        <v>1.113</v>
       </c>
       <c r="M16" s="2" t="n">
         <v>28.829</v>
@@ -1474,7 +1544,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>dcr</t>
         </is>
       </c>
     </row>
@@ -1491,7 +1561,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>full_frozen</t>
+          <t>dcr_frozen</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1500,28 +1570,28 @@
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>79.48</v>
+        <v>77.23</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>85.79000000000001</v>
+        <v>87.41</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>92.06</v>
+        <v>92.01000000000001</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>82.52</v>
+        <v>82.01000000000001</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>70.23</v>
+        <v>69.5</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>77.39</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>29.57</v>
+        <v>29.107</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>1.576</v>
+        <v>1.113</v>
       </c>
       <c r="M17" s="2" t="n">
         <v>28.829</v>
@@ -1530,11 +1600,11 @@
         <v>12.6062</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>1.049e-05</v>
+        <v>2.563e-05</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>dcr</t>
         </is>
       </c>
     </row>
@@ -1551,37 +1621,37 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>full_last2</t>
+          <t>full_frozen</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>98.48999999999999</v>
+        <v>89.98</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>98.34999999999999</v>
+        <v>91.91</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>99.61</v>
+        <v>99.09</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>98.42</v>
+        <v>90.94</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>96.89</v>
+        <v>83.38</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>98.2</v>
+        <v>90.45</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>29.57</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>27.456</v>
+        <v>1.576</v>
       </c>
       <c r="M18" s="2" t="n">
         <v>28.829</v>
@@ -1590,7 +1660,7 @@
         <v>12.6062</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>4.911e-05</v>
+        <v>2.48e-05</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
@@ -1611,37 +1681,37 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>full_last2</t>
+          <t>full_frozen</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>90.31999999999999</v>
+        <v>79.48</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>92.59999999999999</v>
+        <v>85.79000000000001</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>99.14</v>
+        <v>92.06</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>91.44</v>
+        <v>82.52</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>84.23999999999999</v>
+        <v>70.23</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>90.98999999999999</v>
+        <v>77.39</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>29.57</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>27.456</v>
+        <v>1.576</v>
       </c>
       <c r="M19" s="2" t="n">
         <v>28.829</v>
@@ -1650,7 +1720,7 @@
         <v>12.6062</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>2.098e-05</v>
+        <v>1.049e-05</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
@@ -1676,26 +1746,26 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>79.56</v>
+        <v>98.48999999999999</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>87.75</v>
+        <v>98.34999999999999</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>92.56</v>
+        <v>99.61</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>83.45</v>
+        <v>98.42</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>71.59999999999999</v>
+        <v>96.89</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>78.66</v>
+        <v>98.2</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>29.57</v>
@@ -1710,7 +1780,7 @@
         <v>12.6062</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>5.484e-06</v>
+        <v>4.911e-05</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
@@ -1736,26 +1806,26 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>94.34999999999999</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>95.95</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>99.62</v>
+        <v>99.14</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>95.14</v>
+        <v>91.44</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>90.73999999999999</v>
+        <v>84.23999999999999</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>94.94</v>
+        <v>90.98999999999999</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>29.57</v>
@@ -1770,7 +1840,7 @@
         <v>12.6062</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>1.049e-05</v>
+        <v>2.098e-05</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
@@ -1791,37 +1861,37 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>no_residual</t>
+          <t>full_last2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E22" s="2" t="n">
-        <v>89.25</v>
+        <v>79.56</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>92.87</v>
+        <v>87.75</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>99.09999999999999</v>
+        <v>92.56</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>91.02</v>
+        <v>83.45</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>83.52</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>90.55</v>
+        <v>78.66</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>29.57</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>1.576</v>
+        <v>27.456</v>
       </c>
       <c r="M22" s="2" t="n">
         <v>28.829</v>
@@ -1830,7 +1900,7 @@
         <v>12.6062</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>2.48e-05</v>
+        <v>5.484e-06</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
@@ -1851,37 +1921,37 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>no_residual</t>
+          <t>full_last2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E23" s="2" t="n">
-        <v>76.72</v>
+        <v>94.34999999999999</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>87.23</v>
+        <v>95.95</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>91.86</v>
+        <v>99.62</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>81.63</v>
+        <v>95.14</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>68.97</v>
+        <v>90.73999999999999</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>76.43000000000001</v>
+        <v>94.94</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>29.57</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>1.576</v>
+        <v>27.456</v>
       </c>
       <c r="M23" s="2" t="n">
         <v>28.829</v>
@@ -1890,7 +1960,7 @@
         <v>12.6062</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>2.861e-06</v>
+        <v>1.049e-05</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
@@ -1906,38 +1976,42 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Run3</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
+          <t>Run2</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>no_residual</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E24" s="2" t="n">
-        <v>98.40000000000001</v>
+        <v>89.25</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>98.42</v>
+        <v>92.87</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>99.61</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>98.41</v>
+        <v>91.02</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>96.87</v>
+        <v>83.52</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>98.18000000000001</v>
+        <v>90.55</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>29.571</v>
+        <v>29.57</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>27.457</v>
+        <v>1.576</v>
       </c>
       <c r="M24" s="2" t="n">
         <v>28.829</v>
@@ -1946,7 +2020,7 @@
         <v>12.6062</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>7.248e-05</v>
+        <v>2.48e-05</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
@@ -1962,38 +2036,42 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Run3</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr"/>
+          <t>Run2</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>no_residual</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>90.45999999999999</v>
+        <v>76.72</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>92.25</v>
+        <v>87.23</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>99.13</v>
+        <v>91.86</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>91.34999999999999</v>
+        <v>81.63</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>84.06999999999999</v>
+        <v>68.97</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>90.89</v>
+        <v>76.43000000000001</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>29.571</v>
+        <v>29.57</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>27.457</v>
+        <v>1.576</v>
       </c>
       <c r="M25" s="2" t="n">
         <v>28.829</v>
@@ -2002,7 +2080,7 @@
         <v>12.6062</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>2.003e-05</v>
+        <v>2.861e-06</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
@@ -2024,26 +2102,26 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E26" s="2" t="n">
-        <v>79.44</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>87.14</v>
+        <v>98.42</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>92.39</v>
+        <v>99.61</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>83.11</v>
+        <v>98.41</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>71.09999999999999</v>
+        <v>96.87</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>78.20999999999999</v>
+        <v>98.18000000000001</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>29.571</v>
@@ -2058,7 +2136,7 @@
         <v>12.6062</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>1.335e-05</v>
+        <v>7.248e-05</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
@@ -2080,26 +2158,26 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E27" s="2" t="n">
-        <v>93.88</v>
+        <v>90.45999999999999</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>96.08</v>
+        <v>92.25</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>99.61</v>
+        <v>99.13</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>94.97</v>
+        <v>91.34999999999999</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>90.42</v>
+        <v>84.06999999999999</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>94.77</v>
+        <v>90.89</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>29.571</v>
@@ -2114,7 +2192,7 @@
         <v>12.6062</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>1.049e-05</v>
+        <v>2.003e-05</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
@@ -2130,35 +2208,35 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E28" s="2" t="n">
-        <v>98.44</v>
+        <v>79.44</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>98.34999999999999</v>
+        <v>87.14</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>99.59999999999999</v>
+        <v>92.39</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>98.39</v>
+        <v>83.11</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>96.84</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>98.17</v>
+        <v>78.20999999999999</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>29.57</v>
+        <v>29.571</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>27.457</v>
@@ -2170,7 +2248,7 @@
         <v>12.6062</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>3.815e-05</v>
+        <v>1.335e-05</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
@@ -2186,35 +2264,35 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Run4</t>
+          <t>Run3</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E29" s="2" t="n">
-        <v>90.23</v>
+        <v>93.88</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>92.69</v>
+        <v>96.08</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>99.14</v>
+        <v>99.61</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>91.45</v>
+        <v>94.97</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>84.23999999999999</v>
+        <v>90.42</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>90.98999999999999</v>
+        <v>94.77</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>29.57</v>
+        <v>29.571</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>27.457</v>
@@ -2226,7 +2304,7 @@
         <v>12.6062</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>2.766e-05</v>
+        <v>1.049e-05</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
@@ -2248,26 +2326,26 @@
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E30" s="2" t="n">
-        <v>79.19</v>
+        <v>98.44</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>87.72</v>
+        <v>98.34999999999999</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>92.48</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>83.23999999999999</v>
+        <v>98.39</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>71.29000000000001</v>
+        <v>96.84</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>78.41</v>
+        <v>98.17</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>29.57</v>
@@ -2282,7 +2360,7 @@
         <v>12.6062</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>1.049e-05</v>
+        <v>3.815e-05</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
@@ -2304,26 +2382,26 @@
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E31" s="2" t="n">
-        <v>93.7</v>
+        <v>90.23</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>96.5</v>
+        <v>92.69</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>99.62</v>
+        <v>99.14</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>95.08</v>
+        <v>91.45</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>90.62</v>
+        <v>84.23999999999999</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>94.88</v>
+        <v>90.98999999999999</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>29.57</v>
@@ -2338,7 +2416,7 @@
         <v>12.6062</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>8.583000000000001e-06</v>
+        <v>2.766e-05</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
@@ -2354,42 +2432,38 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Run5</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>C1_swap_only</t>
-        </is>
-      </c>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E32" s="2" t="n">
-        <v>90.43000000000001</v>
+        <v>79.19</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>92.45</v>
+        <v>87.72</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>99.14</v>
+        <v>92.48</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>91.43000000000001</v>
+        <v>83.23999999999999</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>84.20999999999999</v>
+        <v>71.29000000000001</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>90.97</v>
+        <v>78.41</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>29.57</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>27.456</v>
+        <v>27.457</v>
       </c>
       <c r="M32" s="2" t="n">
         <v>28.829</v>
@@ -2398,19 +2472,11 @@
         <v>12.6062</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>1.621e-05</v>
+        <v>1.049e-05</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>full</t>
-        </is>
-      </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>last2</t>
         </is>
       </c>
     </row>
@@ -2422,42 +2488,38 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Run5</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>D0_full_encoder</t>
-        </is>
-      </c>
+          <t>Run4</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E33" s="2" t="n">
-        <v>90.56</v>
+        <v>93.7</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>92.81999999999999</v>
+        <v>96.5</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>99.16</v>
+        <v>99.62</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>91.68000000000001</v>
+        <v>95.08</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>84.63</v>
+        <v>90.62</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>91.23999999999999</v>
+        <v>94.88</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>29.57</v>
       </c>
       <c r="L33" s="2" t="n">
-        <v>29.57</v>
+        <v>27.457</v>
       </c>
       <c r="M33" s="2" t="n">
         <v>28.829</v>
@@ -2466,17 +2528,9 @@
         <v>12.6062</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>1.431e-05</v>
+        <v>8.583000000000001e-06</v>
       </c>
       <c r="P33" t="inlineStr">
-        <is>
-          <t>full</t>
-        </is>
-      </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" t="inlineStr">
         <is>
           <t>full</t>
         </is>
@@ -2495,7 +2549,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>M1_BOTR</t>
+          <t>C1_swap_only</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2504,28 +2558,28 @@
         </is>
       </c>
       <c r="E34" s="2" t="n">
-        <v>90.45999999999999</v>
+        <v>90.43000000000001</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>92.44</v>
+        <v>92.45</v>
       </c>
       <c r="G34" s="2" t="n">
         <v>99.14</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>91.44</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>84.23</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>90.98999999999999</v>
+        <v>90.97</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>30.032</v>
+        <v>29.57</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>27.918</v>
+        <v>27.456</v>
       </c>
       <c r="M34" s="2" t="n">
         <v>28.829</v>
@@ -2534,7 +2588,7 @@
         <v>12.6062</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>1.526e-05</v>
+        <v>1.621e-05</v>
       </c>
       <c r="P34" t="inlineStr">
         <is>
@@ -2542,7 +2596,7 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -2558,42 +2612,42 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Run6</t>
+          <t>Run5</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>M1_NSCR_high2</t>
+          <t>D0_full_encoder</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E35" s="2" t="n">
-        <v>98.42</v>
+        <v>90.56</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>98.36</v>
+        <v>92.81999999999999</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>99.59999999999999</v>
+        <v>99.16</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>98.39</v>
+        <v>91.68000000000001</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>96.83</v>
+        <v>84.63</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>98.16</v>
+        <v>91.23999999999999</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>29.572</v>
+        <v>29.57</v>
       </c>
       <c r="L35" s="2" t="n">
-        <v>27.458</v>
+        <v>29.57</v>
       </c>
       <c r="M35" s="2" t="n">
         <v>28.829</v>
@@ -2602,7 +2656,7 @@
         <v>12.6062</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>3.529e-05</v>
+        <v>1.431e-05</v>
       </c>
       <c r="P35" t="inlineStr">
         <is>
@@ -2612,17 +2666,9 @@
       <c r="Q35" t="n">
         <v>0</v>
       </c>
-      <c r="R35" t="n">
-        <v>1</v>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>high2</t>
-        </is>
-      </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>last2</t>
+          <t>full</t>
         </is>
       </c>
     </row>
@@ -2634,12 +2680,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Run6</t>
+          <t>Run5</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>M1_NSCR_high2</t>
+          <t>M1_BOTR</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2648,28 +2694,28 @@
         </is>
       </c>
       <c r="E36" s="2" t="n">
-        <v>90.73</v>
+        <v>90.45999999999999</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>92.08</v>
+        <v>92.44</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>99.13</v>
+        <v>99.14</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>91.40000000000001</v>
+        <v>91.44</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>84.16</v>
+        <v>84.23</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>90.94</v>
+        <v>90.98999999999999</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>29.572</v>
+        <v>30.032</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>27.458</v>
+        <v>27.918</v>
       </c>
       <c r="M36" s="2" t="n">
         <v>28.829</v>
@@ -2678,7 +2724,7 @@
         <v>12.6062</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>2.289e-05</v>
+        <v>1.526e-05</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
@@ -2686,15 +2732,7 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
-      </c>
-      <c r="R36" t="n">
         <v>1</v>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>high2</t>
-        </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -2720,26 +2758,26 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E37" s="2" t="n">
-        <v>79.01000000000001</v>
+        <v>98.42</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>88.23999999999999</v>
+        <v>98.36</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>92.56999999999999</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>83.37</v>
+        <v>98.39</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>71.48</v>
+        <v>96.83</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>78.59999999999999</v>
+        <v>98.16</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>29.572</v>
@@ -2754,7 +2792,7 @@
         <v>12.6062</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>5.722e-06</v>
+        <v>3.529e-05</v>
       </c>
       <c r="P37" t="inlineStr">
         <is>
@@ -2796,26 +2834,26 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E38" s="2" t="n">
-        <v>94.26000000000001</v>
+        <v>90.73</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>95.95999999999999</v>
+        <v>92.08</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>99.61</v>
+        <v>99.13</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>95.09999999999999</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>90.66</v>
+        <v>84.16</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>94.90000000000001</v>
+        <v>90.94</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>29.572</v>
@@ -2830,7 +2868,7 @@
         <v>12.6062</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>1.526e-05</v>
+        <v>2.289e-05</v>
       </c>
       <c r="P38" t="inlineStr">
         <is>
@@ -2862,51 +2900,51 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run6</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>C0_Bilinear_D158</t>
+          <t>M1_NSCR_high2</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>SYSU-CD-256</t>
         </is>
       </c>
       <c r="E39" s="2" t="n">
-        <v>91.16</v>
+        <v>79.01000000000001</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>91.64</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>99.13</v>
+        <v>92.56999999999999</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>91.40000000000001</v>
+        <v>83.37</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>84.16</v>
+        <v>71.48</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>90.94</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>29.542</v>
+        <v>29.572</v>
       </c>
       <c r="L39" s="2" t="n">
-        <v>27.428</v>
+        <v>27.458</v>
       </c>
       <c r="M39" s="2" t="n">
-        <v>28.814</v>
+        <v>28.829</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>12.5866</v>
+        <v>12.6062</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>1.431e-05</v>
+        <v>5.722e-06</v>
       </c>
       <c r="P39" t="inlineStr">
         <is>
@@ -2917,7 +2955,7 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -2928,17 +2966,6 @@
         <is>
           <t>last2</t>
         </is>
-      </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>bilinear</t>
-        </is>
-      </c>
-      <c r="V39" t="n">
-        <v>0</v>
-      </c>
-      <c r="W39" t="n">
-        <v>158</v>
       </c>
     </row>
     <row r="40">
@@ -2949,12 +2976,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Run7</t>
+          <t>Run6</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>C0_Bilinear_D158</t>
+          <t>M1_NSCR_high2</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2963,37 +2990,37 @@
         </is>
       </c>
       <c r="E40" s="2" t="n">
-        <v>94.23999999999999</v>
+        <v>94.26000000000001</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>96.20999999999999</v>
+        <v>95.95999999999999</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>99.62</v>
+        <v>99.61</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>95.22</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>90.87</v>
+        <v>90.66</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>95.02</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>29.542</v>
+        <v>29.572</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>27.428</v>
+        <v>27.458</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>28.814</v>
+        <v>28.829</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>12.5866</v>
+        <v>12.6062</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>1.049e-05</v>
+        <v>1.526e-05</v>
       </c>
       <c r="P40" t="inlineStr">
         <is>
@@ -3004,7 +3031,7 @@
         <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -3015,17 +3042,6 @@
         <is>
           <t>last2</t>
         </is>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>bilinear</t>
-        </is>
-      </c>
-      <c r="V40" t="n">
-        <v>0</v>
-      </c>
-      <c r="W40" t="n">
-        <v>158</v>
       </c>
     </row>
     <row r="41">
@@ -3041,7 +3057,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>C1_PixelShuffle_D158</t>
+          <t>C0_Bilinear_D158</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3050,37 +3066,37 @@
         </is>
       </c>
       <c r="E41" s="2" t="n">
-        <v>90.81999999999999</v>
+        <v>91.16</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>92.23999999999999</v>
+        <v>91.64</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>99.14</v>
+        <v>99.13</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>91.52</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>84.37</v>
+        <v>84.16</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>91.06999999999999</v>
+        <v>90.94</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>29.547</v>
+        <v>29.542</v>
       </c>
       <c r="L41" s="2" t="n">
-        <v>27.433</v>
+        <v>27.428</v>
       </c>
       <c r="M41" s="2" t="n">
-        <v>28.819</v>
+        <v>28.814</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>12.6055</v>
+        <v>12.5866</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>1.669e-05</v>
+        <v>1.431e-05</v>
       </c>
       <c r="P41" t="inlineStr">
         <is>
@@ -3105,7 +3121,7 @@
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>pixelshuffle</t>
+          <t>bilinear</t>
         </is>
       </c>
       <c r="V41" t="n">
@@ -3128,7 +3144,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>C1_PixelShuffle_D158</t>
+          <t>C0_Bilinear_D158</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3137,37 +3153,37 @@
         </is>
       </c>
       <c r="E42" s="2" t="n">
-        <v>93.81999999999999</v>
+        <v>94.23999999999999</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>95.94</v>
+        <v>96.20999999999999</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>99.59999999999999</v>
+        <v>99.62</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>94.87</v>
+        <v>95.22</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>90.23999999999999</v>
+        <v>90.87</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>94.66</v>
+        <v>95.02</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>29.547</v>
+        <v>29.542</v>
       </c>
       <c r="L42" s="2" t="n">
-        <v>27.433</v>
+        <v>27.428</v>
       </c>
       <c r="M42" s="2" t="n">
-        <v>28.819</v>
+        <v>28.814</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>12.6055</v>
+        <v>12.5866</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>1.431e-05</v>
+        <v>1.049e-05</v>
       </c>
       <c r="P42" t="inlineStr">
         <is>
@@ -3192,7 +3208,7 @@
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>pixelshuffle</t>
+          <t>bilinear</t>
         </is>
       </c>
       <c r="V42" t="n">
@@ -3215,7 +3231,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>M1_PBRU_D158</t>
+          <t>C1_PixelShuffle_D158</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3224,28 +3240,28 @@
         </is>
       </c>
       <c r="E43" s="2" t="n">
-        <v>90.39</v>
+        <v>90.81999999999999</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>92.87</v>
+        <v>92.23999999999999</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>99.16</v>
+        <v>99.14</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>91.61</v>
+        <v>91.52</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>84.52</v>
+        <v>84.37</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>91.17</v>
+        <v>91.06999999999999</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>29.548</v>
+        <v>29.547</v>
       </c>
       <c r="L43" s="2" t="n">
-        <v>27.434</v>
+        <v>27.433</v>
       </c>
       <c r="M43" s="2" t="n">
         <v>28.819</v>
@@ -3254,7 +3270,7 @@
         <v>12.6055</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>1.431e-05</v>
+        <v>1.669e-05</v>
       </c>
       <c r="P43" t="inlineStr">
         <is>
@@ -3283,7 +3299,7 @@
         </is>
       </c>
       <c r="V43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
         <v>158</v>
@@ -3302,7 +3318,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>M1_PBRU_D158</t>
+          <t>C1_PixelShuffle_D158</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3311,28 +3327,28 @@
         </is>
       </c>
       <c r="E44" s="2" t="n">
-        <v>93.78</v>
+        <v>93.81999999999999</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>96.38</v>
+        <v>95.94</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>99.61</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>95.06</v>
+        <v>94.87</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>90.59</v>
+        <v>90.23999999999999</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>94.86</v>
+        <v>94.66</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>29.548</v>
+        <v>29.547</v>
       </c>
       <c r="L44" s="2" t="n">
-        <v>27.434</v>
+        <v>27.433</v>
       </c>
       <c r="M44" s="2" t="n">
         <v>28.819</v>
@@ -3341,7 +3357,7 @@
         <v>12.6055</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>1.526e-05</v>
+        <v>1.431e-05</v>
       </c>
       <c r="P44" t="inlineStr">
         <is>
@@ -3370,7 +3386,7 @@
         </is>
       </c>
       <c r="V44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
         <v>158</v>
@@ -3384,12 +3400,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Run8</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>C0_MPCR_Same2</t>
+          <t>M1_PBRU_D158</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3398,34 +3414,34 @@
         </is>
       </c>
       <c r="E45" s="2" t="n">
-        <v>90.67</v>
+        <v>90.39</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>92.04000000000001</v>
+        <v>92.87</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>99.13</v>
+        <v>99.16</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>91.34999999999999</v>
+        <v>91.61</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>84.08</v>
+        <v>84.52</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>90.89</v>
+        <v>91.17</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>29.584</v>
+        <v>29.548</v>
       </c>
       <c r="L45" s="2" t="n">
-        <v>27.47</v>
+        <v>27.434</v>
       </c>
       <c r="M45" s="2" t="n">
-        <v>28.829</v>
+        <v>28.819</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>12.6062</v>
+        <v>12.6055</v>
       </c>
       <c r="O45" s="3" t="n">
         <v>1.431e-05</v>
@@ -3453,22 +3469,14 @@
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>bilinear</t>
+          <t>pixelshuffle</t>
         </is>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W45" t="n">
-        <v>160</v>
-      </c>
-      <c r="X45" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y45" t="inlineStr">
-        <is>
-          <t>same2</t>
-        </is>
+        <v>158</v>
       </c>
     </row>
     <row r="46">
@@ -3479,12 +3487,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Run8</t>
+          <t>Run7</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>C0_MPCR_Same2</t>
+          <t>M1_PBRU_D158</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3493,37 +3501,37 @@
         </is>
       </c>
       <c r="E46" s="2" t="n">
-        <v>93.7</v>
+        <v>93.78</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>96.75</v>
+        <v>96.38</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>99.62</v>
+        <v>99.61</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>95.2</v>
+        <v>95.06</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>90.84</v>
+        <v>90.59</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>95</v>
+        <v>94.86</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>29.584</v>
+        <v>29.548</v>
       </c>
       <c r="L46" s="2" t="n">
-        <v>27.47</v>
+        <v>27.434</v>
       </c>
       <c r="M46" s="2" t="n">
-        <v>28.829</v>
+        <v>28.819</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>12.6062</v>
+        <v>12.6055</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>1.049e-05</v>
+        <v>1.526e-05</v>
       </c>
       <c r="P46" t="inlineStr">
         <is>
@@ -3548,22 +3556,14 @@
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>bilinear</t>
+          <t>pixelshuffle</t>
         </is>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W46" t="n">
-        <v>160</v>
-      </c>
-      <c r="X46" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y46" t="inlineStr">
-        <is>
-          <t>same2</t>
-        </is>
+        <v>158</v>
       </c>
     </row>
     <row r="47">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>M1_MPCR_Multi2</t>
+          <t>C0_MPCR_Same2</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3588,22 +3588,22 @@
         </is>
       </c>
       <c r="E47" s="2" t="n">
-        <v>89.72</v>
+        <v>90.67</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>92.91</v>
+        <v>92.04000000000001</v>
       </c>
       <c r="G47" s="2" t="n">
         <v>99.13</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>91.29000000000001</v>
+        <v>91.34999999999999</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>83.97</v>
+        <v>84.08</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>90.83</v>
+        <v>90.89</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>29.584</v>
@@ -3618,7 +3618,7 @@
         <v>12.6062</v>
       </c>
       <c r="O47" s="3" t="n">
-        <v>1.144e-05</v>
+        <v>1.431e-05</v>
       </c>
       <c r="P47" t="inlineStr">
         <is>
@@ -3657,7 +3657,7 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>multi2</t>
+          <t>same2</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>M1_MPCR_Multi2</t>
+          <t>C0_MPCR_Same2</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3683,22 +3683,22 @@
         </is>
       </c>
       <c r="E48" s="2" t="n">
-        <v>93.90000000000001</v>
+        <v>93.7</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>96.12</v>
+        <v>96.75</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>99.61</v>
+        <v>99.62</v>
       </c>
       <c r="H48" s="2" t="n">
+        <v>95.2</v>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>90.84</v>
+      </c>
+      <c r="J48" s="2" t="n">
         <v>95</v>
-      </c>
-      <c r="I48" s="2" t="n">
-        <v>90.47</v>
-      </c>
-      <c r="J48" s="2" t="n">
-        <v>94.79000000000001</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>29.584</v>
@@ -3713,7 +3713,7 @@
         <v>12.6062</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>1.24e-05</v>
+        <v>1.049e-05</v>
       </c>
       <c r="P48" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>multi2</t>
+          <t>same2</t>
         </is>
       </c>
     </row>
@@ -3764,12 +3764,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Run9</t>
+          <t>Run8</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>C0_FTR_Post</t>
+          <t>M1_MPCR_Multi2</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3778,28 +3778,28 @@
         </is>
       </c>
       <c r="E49" s="2" t="n">
-        <v>90.42</v>
+        <v>89.72</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>92.43000000000001</v>
+        <v>92.91</v>
       </c>
       <c r="G49" s="2" t="n">
         <v>99.13</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>91.42</v>
+        <v>91.29000000000001</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>84.19</v>
+        <v>83.97</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>90.95999999999999</v>
+        <v>90.83</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>29.718</v>
+        <v>29.584</v>
       </c>
       <c r="L49" s="2" t="n">
-        <v>27.604</v>
+        <v>27.47</v>
       </c>
       <c r="M49" s="2" t="n">
         <v>28.829</v>
@@ -3808,7 +3808,7 @@
         <v>12.6062</v>
       </c>
       <c r="O49" s="3" t="n">
-        <v>1.907e-05</v>
+        <v>1.144e-05</v>
       </c>
       <c r="P49" t="inlineStr">
         <is>
@@ -3843,7 +3843,7 @@
         <v>160</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
@@ -3859,12 +3859,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Run9</t>
+          <t>Run8</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>C0_FTR_Post</t>
+          <t>M1_MPCR_Multi2</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3873,28 +3873,28 @@
         </is>
       </c>
       <c r="E50" s="2" t="n">
-        <v>93.94</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>96.01000000000001</v>
+        <v>96.12</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>99.59999999999999</v>
+        <v>99.61</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>94.95999999999999</v>
+        <v>95</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>90.40000000000001</v>
+        <v>90.47</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>94.75</v>
+        <v>94.79000000000001</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>29.718</v>
+        <v>29.584</v>
       </c>
       <c r="L50" s="2" t="n">
-        <v>27.604</v>
+        <v>27.47</v>
       </c>
       <c r="M50" s="2" t="n">
         <v>28.829</v>
@@ -3903,7 +3903,7 @@
         <v>12.6062</v>
       </c>
       <c r="O50" s="3" t="n">
-        <v>6.199e-06</v>
+        <v>1.24e-05</v>
       </c>
       <c r="P50" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>160</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>M1_BiFTR</t>
+          <t>C0_FTR_Post</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3968,28 +3968,28 @@
         </is>
       </c>
       <c r="E51" s="2" t="n">
-        <v>90.37</v>
+        <v>90.42</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>92.59999999999999</v>
+        <v>92.43000000000001</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>99.14</v>
+        <v>99.13</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>91.47</v>
+        <v>91.42</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>84.28</v>
+        <v>84.19</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>91.02</v>
+        <v>90.95999999999999</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>29.755</v>
+        <v>29.718</v>
       </c>
       <c r="L51" s="2" t="n">
-        <v>27.641</v>
+        <v>27.604</v>
       </c>
       <c r="M51" s="2" t="n">
         <v>28.829</v>
@@ -3998,7 +3998,7 @@
         <v>12.6062</v>
       </c>
       <c r="O51" s="3" t="n">
-        <v>2.384e-05</v>
+        <v>1.907e-05</v>
       </c>
       <c r="P51" t="inlineStr">
         <is>
@@ -4054,7 +4054,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>M1_BiFTR</t>
+          <t>C0_FTR_Post</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -4063,28 +4063,28 @@
         </is>
       </c>
       <c r="E52" s="2" t="n">
-        <v>93.90000000000001</v>
+        <v>93.94</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>96.25</v>
+        <v>96.01000000000001</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>99.61</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>95.06</v>
+        <v>94.95999999999999</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>90.59</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>94.86</v>
+        <v>94.75</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>29.755</v>
+        <v>29.718</v>
       </c>
       <c r="L52" s="2" t="n">
-        <v>27.641</v>
+        <v>27.604</v>
       </c>
       <c r="M52" s="2" t="n">
         <v>28.829</v>
@@ -4093,7 +4093,7 @@
         <v>12.6062</v>
       </c>
       <c r="O52" s="3" t="n">
-        <v>1.144e-05</v>
+        <v>6.199e-06</v>
       </c>
       <c r="P52" t="inlineStr">
         <is>
@@ -4139,96 +4139,192 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>TAR-DCR</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr"/>
+          <t>Run9</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>M1_BiFTR</t>
+        </is>
+      </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>CDD-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E53" s="2" t="n">
-        <v>98.69</v>
+        <v>90.37</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>98.89</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>99.7</v>
+        <v>99.14</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>98.79000000000001</v>
+        <v>91.47</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>97.61</v>
+        <v>84.28</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>98.62</v>
+        <v>91.02</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>36.081</v>
-      </c>
-      <c r="L53" s="2" t="n"/>
+        <v>29.755</v>
+      </c>
+      <c r="L53" s="2" t="n">
+        <v>27.641</v>
+      </c>
       <c r="M53" s="2" t="n">
-        <v>36.081</v>
+        <v>28.829</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>16.2593</v>
-      </c>
-      <c r="O53" s="3" t="n"/>
+        <v>12.6062</v>
+      </c>
+      <c r="O53" s="3" t="n">
+        <v>2.384e-05</v>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>high2</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>last2</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>bilinear</t>
+        </is>
+      </c>
+      <c r="V53" t="n">
+        <v>0</v>
+      </c>
+      <c r="W53" t="n">
+        <v>160</v>
+      </c>
+      <c r="X53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>multi2</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>TAR-DCR</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Run1</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr"/>
+          <t>Run9</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>M1_BiFTR</t>
+        </is>
+      </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LEVIR-CD-256</t>
+          <t>WHU-CD-256</t>
         </is>
       </c>
       <c r="E54" s="2" t="n">
-        <v>91.20999999999999</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>93.03</v>
+        <v>96.25</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>99.2</v>
+        <v>99.61</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>92.11</v>
+        <v>95.06</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>85.37</v>
+        <v>90.59</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>91.69</v>
+        <v>94.86</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>36.081</v>
-      </c>
-      <c r="L54" s="2" t="n"/>
+        <v>29.755</v>
+      </c>
+      <c r="L54" s="2" t="n">
+        <v>27.641</v>
+      </c>
       <c r="M54" s="2" t="n">
-        <v>36.081</v>
+        <v>28.829</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>16.2593</v>
-      </c>
-      <c r="O54" s="3" t="n"/>
+        <v>12.6062</v>
+      </c>
+      <c r="O54" s="3" t="n">
+        <v>1.144e-05</v>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>high2</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>last2</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>bilinear</t>
+        </is>
+      </c>
+      <c r="V54" t="n">
+        <v>0</v>
+      </c>
+      <c r="W54" t="n">
+        <v>160</v>
+      </c>
+      <c r="X54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>multi2</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -4244,26 +4340,26 @@
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>SYSU-CD-256</t>
+          <t>CDD-CD-256</t>
         </is>
       </c>
       <c r="E55" s="2" t="n">
-        <v>79.73</v>
+        <v>98.69</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>86.51000000000001</v>
+        <v>98.89</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>92.29000000000001</v>
+        <v>99.7</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>82.98999999999999</v>
+        <v>98.79000000000001</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>70.92</v>
+        <v>97.61</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>78.01000000000001</v>
+        <v>98.62</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>36.081</v>
@@ -4291,26 +4387,26 @@
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>WHU-CD-256</t>
+          <t>LEVIR-CD-256</t>
         </is>
       </c>
       <c r="E56" s="2" t="n">
-        <v>93.28</v>
+        <v>91.20999999999999</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>96.79000000000001</v>
+        <v>93.03</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>99.61</v>
+        <v>99.2</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>95</v>
+        <v>92.11</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>90.47</v>
+        <v>85.37</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>94.8</v>
+        <v>91.69</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>36.081</v>
@@ -4324,8 +4420,102 @@
       </c>
       <c r="O56" s="3" t="n"/>
     </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="n">
+        <v>79.73</v>
+      </c>
+      <c r="F57" s="2" t="n">
+        <v>86.51000000000001</v>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>92.29000000000001</v>
+      </c>
+      <c r="H57" s="2" t="n">
+        <v>82.98999999999999</v>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>70.92</v>
+      </c>
+      <c r="J57" s="2" t="n">
+        <v>78.01000000000001</v>
+      </c>
+      <c r="K57" s="2" t="n">
+        <v>36.081</v>
+      </c>
+      <c r="L57" s="2" t="n"/>
+      <c r="M57" s="2" t="n">
+        <v>36.081</v>
+      </c>
+      <c r="N57" s="2" t="n">
+        <v>16.2593</v>
+      </c>
+      <c r="O57" s="3" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Run1</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>WHU-CD-256</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="n">
+        <v>93.28</v>
+      </c>
+      <c r="F58" s="2" t="n">
+        <v>96.79000000000001</v>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>99.61</v>
+      </c>
+      <c r="H58" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>90.47</v>
+      </c>
+      <c r="J58" s="2" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="K58" s="2" t="n">
+        <v>36.081</v>
+      </c>
+      <c r="L58" s="2" t="n"/>
+      <c r="M58" s="2" t="n">
+        <v>36.081</v>
+      </c>
+      <c r="N58" s="2" t="n">
+        <v>16.2593</v>
+      </c>
+      <c r="O58" s="3" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Y56"/>
+  <autoFilter ref="A1:Y58"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>